--- a/output/MarketNews-202605.xlsx
+++ b/output/MarketNews-202605.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-05" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -810,12 +810,12 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>先端半導体デバイス15品目、31年に224兆円規模へ：AIやデータセンター関連がけん引</t>
+          <t>AIバブル論争に現実味、半導体株ラリーで市場の神経戦は次のステージ</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -849,12 +849,12 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>半導体・AI関連「次の主役」を探る!?</t>
+          <t>Samsung Electronics、車載メモリ半導体で初の世界首位…Micronを6年ぶりに逆転</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C4" s="15" t="n"/>
@@ -866,11 +866,11 @@
       <c r="G4" s="15" t="n"/>
       <c r="H4" s="15" t="n"/>
       <c r="I4" s="15" t="n"/>
-      <c r="J4" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
-      <c r="L4" s="15" t="n"/>
+      <c r="L4" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" s="15" t="n"/>
       <c r="N4" s="15" t="n"/>
       <c r="O4" s="15" t="n"/>
@@ -882,20 +882,18 @@
       <c r="U4" s="15" t="n"/>
       <c r="V4" s="15" t="n"/>
       <c r="W4" s="15" t="n"/>
-      <c r="X4" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X4" s="15" t="n"/>
       <c r="Y4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>キオクシア・太陽誘電etc・・大幅増益期待8銘柄、意外な半導体関連も？</t>
+          <t>三星電子、マイクロン抜き車載半導体で初の世界首位</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -906,7 +904,9 @@
       <c r="F5" s="11" t="n"/>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
+      <c r="I5" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" s="11" t="n"/>
       <c r="K5" s="11" t="n"/>
       <c r="L5" s="12" t="n">
@@ -923,20 +923,18 @@
       <c r="U5" s="11" t="n"/>
       <c r="V5" s="11" t="n"/>
       <c r="W5" s="11" t="n"/>
-      <c r="X5" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X5" s="11" t="n"/>
       <c r="Y5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>ポイントとリスクを整理 好業績の半導体関連銘柄</t>
+          <t>日本をAI・次世代半導体設計の中心へ Tenstorrentが描く成長戦略 | サクセススト－リ－ - 日本の投資環境 - 対日投資</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C6" s="15" t="n"/>
@@ -945,10 +943,14 @@
       </c>
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
+      <c r="J6" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -962,20 +964,18 @@
       <c r="U6" s="15" t="n"/>
       <c r="V6" s="15" t="n"/>
       <c r="W6" s="15" t="n"/>
-      <c r="X6" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X6" s="15" t="n"/>
       <c r="Y6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>半導体メモリー、膨らむ市場期待 世界5社、利益63兆円見通し キオクシア決算に関心</t>
+          <t>半導体製造装置SCREEN、TSMCも頼る個別化・効率化</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
@@ -989,24 +989,5724 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
-      <c r="L7" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
+      <c r="S7" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="T7" s="11" t="n"/>
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="11" t="n"/>
       <c r="W7" s="11" t="n"/>
-      <c r="X7" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X7" s="11" t="n"/>
       <c r="Y7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>AMDがエヌビディアに勝たずとも成功する理由、AI半導体市場の行方</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="15" t="n"/>
+      <c r="S8" s="15" t="n"/>
+      <c r="T8" s="15" t="n"/>
+      <c r="U8" s="15" t="n"/>
+      <c r="V8" s="15" t="n"/>
+      <c r="W8" s="15" t="n"/>
+      <c r="X8" s="15" t="n"/>
+      <c r="Y8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>記憶半導体市場、2027年に1.28兆ドルへ「歴史的」上方修正──AI推論需要で供給不足深刻化</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="11" t="n"/>
+      <c r="S9" s="11" t="n"/>
+      <c r="T9" s="11" t="n"/>
+      <c r="U9" s="11" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="11" t="n"/>
+      <c r="X9" s="11" t="n"/>
+      <c r="Y9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>NISA成長投資枠の次の一手　AI・半導体投資に注目</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="n"/>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="n"/>
+      <c r="R10" s="15" t="n"/>
+      <c r="S10" s="15" t="n"/>
+      <c r="T10" s="15" t="n"/>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="n"/>
+      <c r="W10" s="15" t="n"/>
+      <c r="X10" s="15" t="n"/>
+      <c r="Y10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>NISA成長投資枠の次の一手 AI・半導体投資に注目</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="11" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="11" t="n"/>
+      <c r="T11" s="11" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="W11" s="11" t="n"/>
+      <c r="X11" s="11" t="n"/>
+      <c r="Y11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>【FPGA納期が52週へ急増、CPU価格は3倍に】韓国半導体検査装置メーカーが「供給断絶」の危機に直面</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="15" t="n"/>
+      <c r="S12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="15" t="n"/>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="15" t="n"/>
+      <c r="W12" s="15" t="n"/>
+      <c r="X12" s="15" t="n"/>
+      <c r="Y12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>世界半導体市場は初の150兆円突破というサプライズ！</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n"/>
+      <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="11" t="n"/>
+      <c r="S13" s="11" t="n"/>
+      <c r="T13" s="11" t="n"/>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="W13" s="11" t="n"/>
+      <c r="X13" s="11" t="n"/>
+      <c r="Y13" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>窒化ガリウムと炭化ケイ素のパワー半導体市場調査分析レポート：トップ５企業の生産能力・販売量・平均価格動向</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="15" t="n"/>
+      <c r="S14" s="15" t="n"/>
+      <c r="T14" s="15" t="n"/>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="n"/>
+      <c r="W14" s="15" t="n"/>
+      <c r="X14" s="15" t="n"/>
+      <c r="Y14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>AI相場の次の主役は？ 半導体・ロボット関連銘柄を深掘り</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11" t="n"/>
+      <c r="P15" s="11" t="n"/>
+      <c r="Q15" s="11" t="n"/>
+      <c r="R15" s="11" t="n"/>
+      <c r="S15" s="11" t="n"/>
+      <c r="T15" s="11" t="n"/>
+      <c r="U15" s="11" t="n"/>
+      <c r="V15" s="11" t="n"/>
+      <c r="W15" s="11" t="n"/>
+      <c r="X15" s="11" t="n"/>
+      <c r="Y15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>【材料】 タカノが上値指向鮮明、半導体向け画像処理検査装置でＡＩインフラ需要に照準</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="15" t="n"/>
+      <c r="S16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="15" t="n"/>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="15" t="n"/>
+      <c r="W16" s="15" t="n"/>
+      <c r="X16" s="15" t="n"/>
+      <c r="Y16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>TOTOKU、半導体事業に注力 上田市内の主要製造拠点で生産ライン増強へ</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="11" t="n"/>
+      <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+      <c r="R17" s="11" t="n"/>
+      <c r="S17" s="11" t="n"/>
+      <c r="T17" s="11" t="n"/>
+      <c r="U17" s="11" t="n"/>
+      <c r="V17" s="11" t="n"/>
+      <c r="W17" s="11" t="n"/>
+      <c r="X17" s="11" t="n"/>
+      <c r="Y17" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>AI半導体の高速化を支える“超高多層基板” OKIが新技術を開発</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n"/>
+      <c r="W18" s="15" t="n"/>
+      <c r="X18" s="15" t="n"/>
+      <c r="Y18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>【戸松信博氏「明日の爆騰株」を探せ】レーザーテック：最先端半導体の製造に不可欠な検査装置で「世界シェア100％」 圧倒的な価格決定力で高マージンを維持（マネーポストWEB）</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n"/>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="11" t="n"/>
+      <c r="S19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="11" t="n"/>
+      <c r="U19" s="11" t="n"/>
+      <c r="V19" s="11" t="n"/>
+      <c r="W19" s="11" t="n"/>
+      <c r="X19" s="11" t="n"/>
+      <c r="Y19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>「AIが半導体市場を書き換える」…半導体株が今年75％暴騰（中央日報日本語版）</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="15" t="n"/>
+      <c r="S20" s="15" t="n"/>
+      <c r="T20" s="15" t="n"/>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="15" t="n"/>
+      <c r="W20" s="15" t="n"/>
+      <c r="X20" s="15" t="n"/>
+      <c r="Y20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>【動画】今月の重要ニュース「今年の半導体市場1兆ドル突破が現実的に」</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="11" t="n"/>
+      <c r="R21" s="11" t="n"/>
+      <c r="S21" s="11" t="n"/>
+      <c r="T21" s="11" t="n"/>
+      <c r="U21" s="11" t="n"/>
+      <c r="V21" s="11" t="n"/>
+      <c r="W21" s="11" t="n"/>
+      <c r="X21" s="11" t="n"/>
+      <c r="Y21" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>「AIが半導体市場を書き換える」…半導体株が今年75％暴騰 (中央日報日本語版)</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+      <c r="R22" s="15" t="n"/>
+      <c r="S22" s="15" t="n"/>
+      <c r="T22" s="15" t="n"/>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
+      <c r="W22" s="15" t="n"/>
+      <c r="X22" s="15" t="n"/>
+      <c r="Y22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TSMC・サムスン認めた半導体「超純水」技術 野村マイクロ、10年で株価56倍</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="11" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="11" t="n"/>
+      <c r="R23" s="11" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="11" t="n"/>
+      <c r="U23" s="11" t="n"/>
+      <c r="V23" s="11" t="n"/>
+      <c r="W23" s="11" t="n"/>
+      <c r="X23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>半導体エコシステムにおいて、カスタマイズ型市場インテリジェンスの重要性が高まっている</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="15" t="n"/>
+      <c r="R24" s="15" t="n"/>
+      <c r="S24" s="15" t="n"/>
+      <c r="T24" s="15" t="n"/>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15" t="n"/>
+      <c r="W24" s="15" t="n"/>
+      <c r="X24" s="15" t="n"/>
+      <c r="Y24" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>ＡＩ半導体新興グロック、最大6.5億ドル調達へ 既存投資家から</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="11" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="11" t="n"/>
+      <c r="R25" s="11" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="11" t="n"/>
+      <c r="U25" s="11" t="n"/>
+      <c r="V25" s="11" t="n"/>
+      <c r="W25" s="11" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>NGK、半導体・通信向け開発に2500億円投資 AIの「裏方」に軸足</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="15" t="n"/>
+      <c r="L26" s="15" t="n"/>
+      <c r="M26" s="15" t="n"/>
+      <c r="N26" s="15" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="15" t="n"/>
+      <c r="R26" s="15" t="n"/>
+      <c r="S26" s="15" t="n"/>
+      <c r="T26" s="15" t="n"/>
+      <c r="U26" s="15" t="n"/>
+      <c r="V26" s="15" t="n"/>
+      <c r="W26" s="15" t="n"/>
+      <c r="X26" s="15" t="n"/>
+      <c r="Y26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>アンリツ、OKI、オプトラン…エヌビディアも投資加速！AIデータセンター＆半導体支える「光技術」で“爆需”期待の日本の最強技術企業【厳選8社】</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11" t="n"/>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="11" t="n"/>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="11" t="n"/>
+      <c r="T27" s="11" t="n"/>
+      <c r="U27" s="11" t="n"/>
+      <c r="V27" s="11" t="n"/>
+      <c r="W27" s="11" t="n"/>
+      <c r="X27" s="11" t="n"/>
+      <c r="Y27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>ＡＩ半導体新興グロック、最大6.5億ドル調達へ 既存投資家から(ロイター)</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="15" t="n"/>
+      <c r="M28" s="15" t="n"/>
+      <c r="N28" s="15" t="n"/>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="15" t="n"/>
+      <c r="Q28" s="15" t="n"/>
+      <c r="R28" s="15" t="n"/>
+      <c r="S28" s="15" t="n"/>
+      <c r="T28" s="15" t="n"/>
+      <c r="U28" s="15" t="n"/>
+      <c r="V28" s="15" t="n"/>
+      <c r="W28" s="15" t="n"/>
+      <c r="X28" s="15" t="n"/>
+      <c r="Y28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>ＡＩ半導体新興グロック、最大6.5億ドル調達へ 既存投資家から (ロイター)</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="11" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="11" t="n"/>
+      <c r="R29" s="11" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="11" t="n"/>
+      <c r="U29" s="11" t="n"/>
+      <c r="V29" s="11" t="n"/>
+      <c r="W29" s="11" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>半導体工場「需要ある限り応える」ダイフク、1600億円投資で描く姿とは：FAニュース（1/2 ページ）</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
+      <c r="M30" s="15" t="n"/>
+      <c r="N30" s="15" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="15" t="n"/>
+      <c r="R30" s="15" t="n"/>
+      <c r="S30" s="15" t="n"/>
+      <c r="T30" s="15" t="n"/>
+      <c r="U30" s="15" t="n"/>
+      <c r="V30" s="15" t="n"/>
+      <c r="W30" s="15" t="n"/>
+      <c r="X30" s="15" t="n"/>
+      <c r="Y30" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>AI特需、電子部品に波及 4〜6月の半導体市場はメモリーがけん引役</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="11" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="11" t="n"/>
+      <c r="U31" s="11" t="n"/>
+      <c r="V31" s="11" t="n"/>
+      <c r="W31" s="11" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>AI半導体株に割高感は乏しい、26年下期の日本株の警戒すべき3つのリスクと狙い目「7セクター」</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="15" t="n"/>
+      <c r="Q32" s="15" t="n"/>
+      <c r="R32" s="15" t="n"/>
+      <c r="S32" s="15" t="n"/>
+      <c r="T32" s="15" t="n"/>
+      <c r="U32" s="15" t="n"/>
+      <c r="V32" s="15" t="n"/>
+      <c r="W32" s="15" t="n"/>
+      <c r="X32" s="15" t="n"/>
+      <c r="Y32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>韓国政府とKOTRAが日本でビジネスイベント AI・半導体協力強化へ</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="11" t="n"/>
+      <c r="R33" s="11" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="11" t="n"/>
+      <c r="U33" s="11" t="n"/>
+      <c r="V33" s="11" t="n"/>
+      <c r="W33" s="11" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>【プロが解説】世界シェア9割。東京エレクトロンはなぜ半導体製造で「無敵」であり続けるのか(LIMO)</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
+      <c r="M34" s="15" t="n"/>
+      <c r="N34" s="15" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="15" t="n"/>
+      <c r="Q34" s="15" t="n"/>
+      <c r="R34" s="15" t="n"/>
+      <c r="S34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" s="15" t="n"/>
+      <c r="U34" s="15" t="n"/>
+      <c r="V34" s="15" t="n"/>
+      <c r="W34" s="15" t="n"/>
+      <c r="X34" s="15" t="n"/>
+      <c r="Y34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>日本の半導体メモリメーカー一覧とランキング・関連銘柄・投資先を徹底解説【2026年最新】</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
+      <c r="N35" s="11" t="n"/>
+      <c r="O35" s="11" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="11" t="n"/>
+      <c r="R35" s="11" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="11" t="n"/>
+      <c r="U35" s="11" t="n"/>
+      <c r="V35" s="11" t="n"/>
+      <c r="W35" s="11" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>韓国サムスン、ベトナム初の半導体検査工場計画 15億ドル投資</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="15" t="n"/>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="15" t="n"/>
+      <c r="S36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="15" t="n"/>
+      <c r="U36" s="15" t="n"/>
+      <c r="V36" s="15" t="n"/>
+      <c r="W36" s="15" t="n"/>
+      <c r="X36" s="15" t="n"/>
+      <c r="Y36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>韓国サムスン、ベトナム初の半導体検査工場計画 15億ドル投資(ロイター)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="11" t="n"/>
+      <c r="R37" s="11" t="n"/>
+      <c r="S37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="11" t="n"/>
+      <c r="U37" s="11" t="n"/>
+      <c r="V37" s="11" t="n"/>
+      <c r="W37" s="11" t="n"/>
+      <c r="X37" s="11" t="n"/>
+      <c r="Y37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>韓国サムスン、ベトナム初の半導体検査工場計画 15億ドル投資（ロイター）</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="n"/>
+      <c r="M38" s="15" t="n"/>
+      <c r="N38" s="15" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="15" t="n"/>
+      <c r="Q38" s="15" t="n"/>
+      <c r="R38" s="15" t="n"/>
+      <c r="S38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="15" t="n"/>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="15" t="n"/>
+      <c r="W38" s="15" t="n"/>
+      <c r="X38" s="15" t="n"/>
+      <c r="Y38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>ネオセムの子会社が115億ウォン規模の半導体検査装置受注を獲得、株価は5%下落</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="O39" s="11" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="11" t="n"/>
+      <c r="R39" s="11" t="n"/>
+      <c r="S39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" s="11" t="n"/>
+      <c r="U39" s="11" t="n"/>
+      <c r="V39" s="11" t="n"/>
+      <c r="W39" s="11" t="n"/>
+      <c r="X39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>トレックス・セミコンダクター（6616）、半導体市場回復を捉えさらなる成長へ 27年3月期は売上高・営業利益共に2桁増を計画</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="15" t="n"/>
+      <c r="L40" s="15" t="n"/>
+      <c r="M40" s="15" t="n"/>
+      <c r="N40" s="15" t="n"/>
+      <c r="O40" s="15" t="n"/>
+      <c r="P40" s="15" t="n"/>
+      <c r="Q40" s="15" t="n"/>
+      <c r="R40" s="15" t="n"/>
+      <c r="S40" s="15" t="n"/>
+      <c r="T40" s="15" t="n"/>
+      <c r="U40" s="15" t="n"/>
+      <c r="V40" s="15" t="n"/>
+      <c r="W40" s="15" t="n"/>
+      <c r="X40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>「半導体」がランキング首位に輝く、世界的なＡＩ投資拡大でスーパーサイクル突入か＜注目テーマ＞ | 特集 - 株探ニュース</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n"/>
+      <c r="N41" s="11" t="n"/>
+      <c r="O41" s="11" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="11" t="n"/>
+      <c r="R41" s="11" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="11" t="n"/>
+      <c r="U41" s="11" t="n"/>
+      <c r="V41" s="11" t="n"/>
+      <c r="W41" s="11" t="n"/>
+      <c r="X41" s="11" t="n"/>
+      <c r="Y41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>半導体製造装置サプライヤ顧客満足度ランキング2026トップ9、日本勢は5社がランクイン | TECH+（テックプラス）</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
+      <c r="K42" s="15" t="n"/>
+      <c r="L42" s="15" t="n"/>
+      <c r="M42" s="15" t="n"/>
+      <c r="N42" s="15" t="n"/>
+      <c r="O42" s="15" t="n"/>
+      <c r="P42" s="15" t="n"/>
+      <c r="Q42" s="15" t="n"/>
+      <c r="R42" s="15" t="n"/>
+      <c r="S42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="15" t="n"/>
+      <c r="U42" s="15" t="n"/>
+      <c r="V42" s="15" t="n"/>
+      <c r="W42" s="15" t="n"/>
+      <c r="X42" s="15" t="n"/>
+      <c r="Y42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>AI半導体で「パネルは新たなフロンティア」、Lamの装置戦略：大型パネルに求められる技術とは（1/3 ページ）</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="11" t="n"/>
+      <c r="N43" s="11" t="n"/>
+      <c r="O43" s="11" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="11" t="n"/>
+      <c r="R43" s="11" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="11" t="n"/>
+      <c r="U43" s="11" t="n"/>
+      <c r="V43" s="11" t="n"/>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="11" t="n"/>
+      <c r="Y43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>日経平均高値、業績相場へ回帰期待、AI・半導体ブームすそ野拡大で日本に恩恵（窪田真之）</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="15" t="n"/>
+      <c r="L44" s="15" t="n"/>
+      <c r="M44" s="15" t="n"/>
+      <c r="N44" s="15" t="n"/>
+      <c r="O44" s="15" t="n"/>
+      <c r="P44" s="15" t="n"/>
+      <c r="Q44" s="15" t="n"/>
+      <c r="R44" s="15" t="n"/>
+      <c r="S44" s="15" t="n"/>
+      <c r="T44" s="15" t="n"/>
+      <c r="U44" s="15" t="n"/>
+      <c r="V44" s="15" t="n"/>
+      <c r="W44" s="15" t="n"/>
+      <c r="X44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="15" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>2035年のパワー半導体市場は7兆3495億円に倍増、酸化ガリウムが149億円規模に：組み込み開発ニュース</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="11" t="n"/>
+      <c r="N45" s="11" t="n"/>
+      <c r="O45" s="11" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="11" t="n"/>
+      <c r="R45" s="11" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="11" t="n"/>
+      <c r="U45" s="11" t="n"/>
+      <c r="V45" s="11" t="n"/>
+      <c r="W45" s="11" t="n"/>
+      <c r="X45" s="11" t="n"/>
+      <c r="Y45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>混戦するAI半導体市場、“NVIDIAの牙城”崩す競合チップが台頭 「新CPU」で巻き返せるか</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
+      <c r="N46" s="15" t="n"/>
+      <c r="O46" s="15" t="n"/>
+      <c r="P46" s="15" t="n"/>
+      <c r="Q46" s="15" t="n"/>
+      <c r="R46" s="15" t="n"/>
+      <c r="S46" s="15" t="n"/>
+      <c r="T46" s="15" t="n"/>
+      <c r="U46" s="15" t="n"/>
+      <c r="V46" s="15" t="n"/>
+      <c r="W46" s="15" t="n"/>
+      <c r="X46" s="15" t="n"/>
+      <c r="Y46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>AI半導体景気に死角はないか カギを握る韓国・台湾の受注・在庫動向 野村CIO・宮嵜浩</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="11" t="n"/>
+      <c r="N47" s="11" t="n"/>
+      <c r="O47" s="11" t="n"/>
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="11" t="n"/>
+      <c r="R47" s="11" t="n"/>
+      <c r="S47" s="11" t="n"/>
+      <c r="T47" s="11" t="n"/>
+      <c r="U47" s="11" t="n"/>
+      <c r="V47" s="11" t="n"/>
+      <c r="W47" s="11" t="n"/>
+      <c r="X47" s="11" t="n"/>
+      <c r="Y47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>AI・半導体主導の買い継続、関連セクターへ連想買い波及【今日の市場はどう動いた？】</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="15" t="n"/>
+      <c r="J48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="15" t="n"/>
+      <c r="L48" s="15" t="n"/>
+      <c r="M48" s="15" t="n"/>
+      <c r="N48" s="15" t="n"/>
+      <c r="O48" s="15" t="n"/>
+      <c r="P48" s="15" t="n"/>
+      <c r="Q48" s="15" t="n"/>
+      <c r="R48" s="15" t="n"/>
+      <c r="S48" s="15" t="n"/>
+      <c r="T48" s="15" t="n"/>
+      <c r="U48" s="15" t="n"/>
+      <c r="V48" s="15" t="n"/>
+      <c r="W48" s="15" t="n"/>
+      <c r="X48" s="15" t="n"/>
+      <c r="Y48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>AI投資、台湾へ100億ドル AMD、半導体性能向上へ</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="11" t="n"/>
+      <c r="N49" s="11" t="n"/>
+      <c r="O49" s="11" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="11" t="n"/>
+      <c r="R49" s="11" t="n"/>
+      <c r="S49" s="11" t="n"/>
+      <c r="T49" s="11" t="n"/>
+      <c r="U49" s="11" t="n"/>
+      <c r="V49" s="11" t="n"/>
+      <c r="W49" s="11" t="n"/>
+      <c r="X49" s="11" t="n"/>
+      <c r="Y49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>ラムリサーチ、半導体製造装置にＡＩ導入へ 米事業拡大も＝ＣＥＯ（ロイター）</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="15" t="n"/>
+      <c r="J50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="15" t="n"/>
+      <c r="L50" s="15" t="n"/>
+      <c r="M50" s="15" t="n"/>
+      <c r="N50" s="15" t="n"/>
+      <c r="O50" s="15" t="n"/>
+      <c r="P50" s="15" t="n"/>
+      <c r="Q50" s="15" t="n"/>
+      <c r="R50" s="15" t="n"/>
+      <c r="S50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="15" t="n"/>
+      <c r="U50" s="15" t="n"/>
+      <c r="V50" s="15" t="n"/>
+      <c r="W50" s="15" t="n"/>
+      <c r="X50" s="15" t="n"/>
+      <c r="Y50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>ラムリサーチ、半導体製造装置にＡＩ導入へ 米事業拡大も＝ＣＥＯ (ロイター)</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="11" t="n"/>
+      <c r="N51" s="11" t="n"/>
+      <c r="O51" s="11" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="11" t="n"/>
+      <c r="R51" s="11" t="n"/>
+      <c r="S51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="11" t="n"/>
+      <c r="U51" s="11" t="n"/>
+      <c r="V51" s="11" t="n"/>
+      <c r="W51" s="11" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>ラムリサーチ、半導体製造装置にＡＩ導入へ 米事業拡大も＝ＣＥＯ(ロイター)</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="15" t="n"/>
+      <c r="J52" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="15" t="n"/>
+      <c r="L52" s="15" t="n"/>
+      <c r="M52" s="15" t="n"/>
+      <c r="N52" s="15" t="n"/>
+      <c r="O52" s="15" t="n"/>
+      <c r="P52" s="15" t="n"/>
+      <c r="Q52" s="15" t="n"/>
+      <c r="R52" s="15" t="n"/>
+      <c r="S52" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="15" t="n"/>
+      <c r="U52" s="15" t="n"/>
+      <c r="V52" s="15" t="n"/>
+      <c r="W52" s="15" t="n"/>
+      <c r="X52" s="15" t="n"/>
+      <c r="Y52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>ASML、インドで半導体製造支援 タタ傘下と提携</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="11" t="n"/>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="11" t="n"/>
+      <c r="N53" s="11" t="n"/>
+      <c r="O53" s="11" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="11" t="n"/>
+      <c r="R53" s="11" t="n"/>
+      <c r="S53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" s="11" t="n"/>
+      <c r="U53" s="11" t="n"/>
+      <c r="V53" s="11" t="n"/>
+      <c r="W53" s="11" t="n"/>
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>半導体の計測と検査業界動向：2026年の市場規模は21090百万米ドル見込み</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="15" t="n"/>
+      <c r="J54" s="15" t="n"/>
+      <c r="K54" s="15" t="n"/>
+      <c r="L54" s="15" t="n"/>
+      <c r="M54" s="15" t="n"/>
+      <c r="N54" s="15" t="n"/>
+      <c r="O54" s="15" t="n"/>
+      <c r="P54" s="15" t="n"/>
+      <c r="Q54" s="15" t="n"/>
+      <c r="R54" s="15" t="n"/>
+      <c r="S54" s="15" t="n"/>
+      <c r="T54" s="15" t="n"/>
+      <c r="U54" s="15" t="n"/>
+      <c r="V54" s="15" t="n"/>
+      <c r="W54" s="15" t="n"/>
+      <c r="X54" s="15" t="n"/>
+      <c r="Y54" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>AI半導体市場は2031年に130兆円規模へ、HBMとAIアクセラレータがけん引 富士キメラ総研予測 | TECH+（テックプラス）</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="11" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="11" t="n"/>
+      <c r="N55" s="11" t="n"/>
+      <c r="O55" s="11" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="11" t="n"/>
+      <c r="R55" s="11" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="11" t="n"/>
+      <c r="U55" s="11" t="n"/>
+      <c r="V55" s="11" t="n"/>
+      <c r="W55" s="11" t="n"/>
+      <c r="X55" s="11" t="n"/>
+      <c r="Y55" s="11" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>世界の半導体市場、当面は供給逼迫続く見通し＝ＡＳＭＬ・ＣＥＯ（ロイター）</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="15" t="n"/>
+      <c r="I56" s="15" t="n"/>
+      <c r="J56" s="15" t="n"/>
+      <c r="K56" s="15" t="n"/>
+      <c r="L56" s="15" t="n"/>
+      <c r="M56" s="15" t="n"/>
+      <c r="N56" s="15" t="n"/>
+      <c r="O56" s="15" t="n"/>
+      <c r="P56" s="15" t="n"/>
+      <c r="Q56" s="15" t="n"/>
+      <c r="R56" s="15" t="n"/>
+      <c r="S56" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="15" t="n"/>
+      <c r="U56" s="15" t="n"/>
+      <c r="V56" s="15" t="n"/>
+      <c r="W56" s="15" t="n"/>
+      <c r="X56" s="15" t="n"/>
+      <c r="Y56" s="15" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>AMD、台湾に100億ドル超を投資 AI半導体でASEなどと連携</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="11" t="n"/>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="11" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="11" t="n"/>
+      <c r="M57" s="11" t="n"/>
+      <c r="N57" s="11" t="n"/>
+      <c r="O57" s="11" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="11" t="n"/>
+      <c r="R57" s="11" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="11" t="n"/>
+      <c r="U57" s="11" t="n"/>
+      <c r="V57" s="11" t="n"/>
+      <c r="W57" s="11" t="n"/>
+      <c r="X57" s="11" t="n"/>
+      <c r="Y57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>エヌビディア好決算でAI半導体投資の強気継続【今日の市場はどう動いた？】</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="15" t="n"/>
+      <c r="J58" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="15" t="n"/>
+      <c r="L58" s="15" t="n"/>
+      <c r="M58" s="15" t="n"/>
+      <c r="N58" s="15" t="n"/>
+      <c r="O58" s="15" t="n"/>
+      <c r="P58" s="15" t="n"/>
+      <c r="Q58" s="15" t="n"/>
+      <c r="R58" s="15" t="n"/>
+      <c r="S58" s="15" t="n"/>
+      <c r="T58" s="15" t="n"/>
+      <c r="U58" s="15" t="n"/>
+      <c r="V58" s="15" t="n"/>
+      <c r="W58" s="15" t="n"/>
+      <c r="X58" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="15" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>【米国株人気ランキング】AI・半導体に強い関心、個人投資家は何を買った？</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="11" t="n"/>
+      <c r="G59" s="11" t="n"/>
+      <c r="H59" s="11" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="11" t="n"/>
+      <c r="M59" s="11" t="n"/>
+      <c r="N59" s="11" t="n"/>
+      <c r="O59" s="11" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="11" t="n"/>
+      <c r="R59" s="11" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="11" t="n"/>
+      <c r="U59" s="11" t="n"/>
+      <c r="V59" s="11" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="11" t="n"/>
+      <c r="Y59" s="11" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>【米国株人気ランキング】AI・半導体に強い関心、個人投資家は何を買った？ (マイナビニュース)</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="15" t="n"/>
+      <c r="J60" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="15" t="n"/>
+      <c r="L60" s="15" t="n"/>
+      <c r="M60" s="15" t="n"/>
+      <c r="N60" s="15" t="n"/>
+      <c r="O60" s="15" t="n"/>
+      <c r="P60" s="15" t="n"/>
+      <c r="Q60" s="15" t="n"/>
+      <c r="R60" s="15" t="n"/>
+      <c r="S60" s="15" t="n"/>
+      <c r="T60" s="15" t="n"/>
+      <c r="U60" s="15" t="n"/>
+      <c r="V60" s="15" t="n"/>
+      <c r="W60" s="15" t="n"/>
+      <c r="X60" s="15" t="n"/>
+      <c r="Y60" s="15" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>ラムリサーチ、半導体製造装置にＡＩ導入へ 米事業拡大も＝ＣＥＯ</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n"/>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="11" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="11" t="n"/>
+      <c r="O61" s="11" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="11" t="n"/>
+      <c r="R61" s="11" t="n"/>
+      <c r="S61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" s="11" t="n"/>
+      <c r="U61" s="11" t="n"/>
+      <c r="V61" s="11" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="11" t="n"/>
+      <c r="Y61" s="11" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>半導体計測検査装置市場、AI半導体・次世代チップ検査需要を追い風に2035年まで高成長CAGR6.9％へ</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="15" t="n"/>
+      <c r="J62" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="15" t="n"/>
+      <c r="L62" s="15" t="n"/>
+      <c r="M62" s="15" t="n"/>
+      <c r="N62" s="15" t="n"/>
+      <c r="O62" s="15" t="n"/>
+      <c r="P62" s="15" t="n"/>
+      <c r="Q62" s="15" t="n"/>
+      <c r="R62" s="15" t="n"/>
+      <c r="S62" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" s="15" t="n"/>
+      <c r="U62" s="15" t="n"/>
+      <c r="V62" s="15" t="n"/>
+      <c r="W62" s="15" t="n"/>
+      <c r="X62" s="15" t="n"/>
+      <c r="Y62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>世界の半導体市場、当面は供給逼迫続く見通し＝ＡＳＭＬ・ＣＥＯ</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="11" t="n"/>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="11" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="11" t="n"/>
+      <c r="O63" s="11" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="11" t="n"/>
+      <c r="R63" s="11" t="n"/>
+      <c r="S63" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" s="11" t="n"/>
+      <c r="U63" s="11" t="n"/>
+      <c r="V63" s="11" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="11" t="n"/>
+      <c r="Y63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>半導体工場の細い配管や下水管もロボで検査 ソラリス、5億円調達</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15" t="n"/>
+      <c r="F64" s="15" t="n"/>
+      <c r="G64" s="15" t="n"/>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="15" t="n"/>
+      <c r="J64" s="15" t="n"/>
+      <c r="K64" s="15" t="n"/>
+      <c r="L64" s="15" t="n"/>
+      <c r="M64" s="15" t="n"/>
+      <c r="N64" s="15" t="n"/>
+      <c r="O64" s="15" t="n"/>
+      <c r="P64" s="15" t="n"/>
+      <c r="Q64" s="15" t="n"/>
+      <c r="R64" s="15" t="n"/>
+      <c r="S64" s="15" t="n"/>
+      <c r="T64" s="15" t="n"/>
+      <c r="U64" s="15" t="n"/>
+      <c r="V64" s="15" t="n"/>
+      <c r="W64" s="15" t="n"/>
+      <c r="X64" s="15" t="n"/>
+      <c r="Y64" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>「年内に製造量3割増へ」半導体検査用部品メーカー『日本電子材料』 菊池市で新工場完成 熊本</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="11" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="n"/>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="11" t="n"/>
+      <c r="O65" s="11" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="11" t="n"/>
+      <c r="R65" s="11" t="n"/>
+      <c r="S65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" s="11" t="n"/>
+      <c r="V65" s="11" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="11" t="n"/>
+      <c r="Y65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>半導体市場、28年にメモリー価格下落で縮小 米ガートナー</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="15" t="n"/>
+      <c r="E66" s="15" t="n"/>
+      <c r="F66" s="15" t="n"/>
+      <c r="G66" s="15" t="n"/>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="15" t="n"/>
+      <c r="J66" s="15" t="n"/>
+      <c r="K66" s="15" t="n"/>
+      <c r="L66" s="15" t="n"/>
+      <c r="M66" s="15" t="n"/>
+      <c r="N66" s="15" t="n"/>
+      <c r="O66" s="15" t="n"/>
+      <c r="P66" s="15" t="n"/>
+      <c r="Q66" s="15" t="n"/>
+      <c r="R66" s="15" t="n"/>
+      <c r="S66" s="15" t="n"/>
+      <c r="T66" s="15" t="n"/>
+      <c r="U66" s="15" t="n"/>
+      <c r="V66" s="15" t="n"/>
+      <c r="W66" s="15" t="n"/>
+      <c r="X66" s="15" t="n"/>
+      <c r="Y66" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>エヌビディアCEO、中国のAI半導体市場は「いずれ開かれる」（Bloomberg）</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="11" t="n"/>
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="11" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="11" t="n"/>
+      <c r="M67" s="11" t="n"/>
+      <c r="N67" s="11" t="n"/>
+      <c r="O67" s="11" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="11" t="n"/>
+      <c r="R67" s="11" t="n"/>
+      <c r="S67" s="11" t="n"/>
+      <c r="T67" s="11" t="n"/>
+      <c r="U67" s="11" t="n"/>
+      <c r="V67" s="11" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="11" t="n"/>
+      <c r="Y67" s="11" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>【米国株動向】AI半導体市場のリーダー、エヌビディア［NVDA］に挑む新興AI銘柄：セレブラス・システムズ［CBRS］</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n"/>
+      <c r="D68" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="15" t="n"/>
+      <c r="F68" s="15" t="n"/>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="15" t="n"/>
+      <c r="J68" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="15" t="n"/>
+      <c r="L68" s="15" t="n"/>
+      <c r="M68" s="15" t="n"/>
+      <c r="N68" s="15" t="n"/>
+      <c r="O68" s="15" t="n"/>
+      <c r="P68" s="15" t="n"/>
+      <c r="Q68" s="15" t="n"/>
+      <c r="R68" s="15" t="n"/>
+      <c r="S68" s="15" t="n"/>
+      <c r="T68" s="15" t="n"/>
+      <c r="U68" s="15" t="n"/>
+      <c r="V68" s="15" t="n"/>
+      <c r="W68" s="15" t="n"/>
+      <c r="X68" s="15" t="n"/>
+      <c r="Y68" s="15" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>25年の世界半導体材料市場は過去最高に、HBM投資など背景：SEMI最新レポート</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="11" t="n"/>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="11" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="11" t="n"/>
+      <c r="O69" s="11" t="n"/>
+      <c r="P69" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="11" t="n"/>
+      <c r="R69" s="11" t="n"/>
+      <c r="S69" s="11" t="n"/>
+      <c r="T69" s="11" t="n"/>
+      <c r="U69" s="11" t="n"/>
+      <c r="V69" s="11" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="11" t="n"/>
+      <c r="Y69" s="11" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>エヌビディアのフアンCEO、中国のAI半導体市場の開放に期待「H200需要は驚異的」</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="n"/>
+      <c r="D70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="15" t="n"/>
+      <c r="F70" s="15" t="n"/>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="15" t="n"/>
+      <c r="J70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="15" t="n"/>
+      <c r="L70" s="15" t="n"/>
+      <c r="M70" s="15" t="n"/>
+      <c r="N70" s="15" t="n"/>
+      <c r="O70" s="15" t="n"/>
+      <c r="P70" s="15" t="n"/>
+      <c r="Q70" s="15" t="n"/>
+      <c r="R70" s="15" t="n"/>
+      <c r="S70" s="15" t="n"/>
+      <c r="T70" s="15" t="n"/>
+      <c r="U70" s="15" t="n"/>
+      <c r="V70" s="15" t="n"/>
+      <c r="W70" s="15" t="n"/>
+      <c r="X70" s="15" t="n"/>
+      <c r="Y70" s="15" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>AI半導体ブーム、自滅の種まく</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="11" t="n"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="11" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="11" t="n"/>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="11" t="n"/>
+      <c r="R71" s="11" t="n"/>
+      <c r="S71" s="11" t="n"/>
+      <c r="T71" s="11" t="n"/>
+      <c r="U71" s="11" t="n"/>
+      <c r="V71" s="11" t="n"/>
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="11" t="n"/>
+      <c r="Y71" s="11" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>編集者の視点「AI関連投資6年で1200兆円、半導体や冷却」 - 日経テックフォーサイト</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="n"/>
+      <c r="D72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="15" t="n"/>
+      <c r="F72" s="15" t="n"/>
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="15" t="n"/>
+      <c r="J72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="15" t="n"/>
+      <c r="L72" s="15" t="n"/>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="15" t="n"/>
+      <c r="O72" s="15" t="n"/>
+      <c r="P72" s="15" t="n"/>
+      <c r="Q72" s="15" t="n"/>
+      <c r="R72" s="15" t="n"/>
+      <c r="S72" s="15" t="n"/>
+      <c r="T72" s="15" t="n"/>
+      <c r="U72" s="15" t="n"/>
+      <c r="V72" s="15" t="n"/>
+      <c r="W72" s="15" t="n"/>
+      <c r="X72" s="15" t="n"/>
+      <c r="Y72" s="15" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>AI・半導体相場は終わったのか？今後カギを握る3つの要因（会社四季報オンライン）</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="11" t="n"/>
+      <c r="F73" s="11" t="n"/>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="11" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="11" t="n"/>
+      <c r="M73" s="11" t="n"/>
+      <c r="N73" s="11" t="n"/>
+      <c r="O73" s="11" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="11" t="n"/>
+      <c r="R73" s="11" t="n"/>
+      <c r="S73" s="11" t="n"/>
+      <c r="T73" s="11" t="n"/>
+      <c r="U73" s="11" t="n"/>
+      <c r="V73" s="11" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="11" t="n"/>
+      <c r="Y73" s="11" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>【記録的な増収増益】キオクシア決算発表で再注目、AI半導体関連銘柄4選</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n"/>
+      <c r="D74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="15" t="n"/>
+      <c r="F74" s="15" t="n"/>
+      <c r="G74" s="15" t="n"/>
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="15" t="n"/>
+      <c r="J74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="15" t="n"/>
+      <c r="L74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="15" t="n"/>
+      <c r="N74" s="15" t="n"/>
+      <c r="O74" s="15" t="n"/>
+      <c r="P74" s="15" t="n"/>
+      <c r="Q74" s="15" t="n"/>
+      <c r="R74" s="15" t="n"/>
+      <c r="S74" s="15" t="n"/>
+      <c r="T74" s="15" t="n"/>
+      <c r="U74" s="15" t="n"/>
+      <c r="V74" s="15" t="n"/>
+      <c r="W74" s="15" t="n"/>
+      <c r="X74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" s="15" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>半導体製造装置メーカー売上高トップ15ランキング、日本勢が過半の8社、半導体企業ランキングと対照的</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="11" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="11" t="n"/>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="11" t="n"/>
+      <c r="R75" s="11" t="n"/>
+      <c r="S75" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" s="11" t="n"/>
+      <c r="U75" s="11" t="n"/>
+      <c r="V75" s="11" t="n"/>
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" s="11" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>ラムリサーチ、半導体多層化の本命に エッチング・成膜に強み</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="15" t="n"/>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="15" t="n"/>
+      <c r="J76" s="15" t="n"/>
+      <c r="K76" s="15" t="n"/>
+      <c r="L76" s="15" t="n"/>
+      <c r="M76" s="15" t="n"/>
+      <c r="N76" s="15" t="n"/>
+      <c r="O76" s="15" t="n"/>
+      <c r="P76" s="15" t="n"/>
+      <c r="Q76" s="15" t="n"/>
+      <c r="R76" s="15" t="n"/>
+      <c r="S76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" s="15" t="n"/>
+      <c r="U76" s="15" t="n"/>
+      <c r="V76" s="15" t="n"/>
+      <c r="W76" s="15" t="n"/>
+      <c r="X76" s="15" t="n"/>
+      <c r="Y76" s="15" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>エヌビディアCEO、中国のAI半導体市場は「いずれ開かれる」</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="11" t="n"/>
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="11" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="11" t="n"/>
+      <c r="O77" s="11" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="11" t="n"/>
+      <c r="R77" s="11" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="11" t="n"/>
+      <c r="U77" s="11" t="n"/>
+      <c r="V77" s="11" t="n"/>
+      <c r="W77" s="11" t="n"/>
+      <c r="X77" s="11" t="n"/>
+      <c r="Y77" s="11" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>AI・半導体株の「急調整」にどう対応する？激動相場で失敗しないための「投資と投機」の境界線／松本史雄氏【月曜マネーLIVE】</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n"/>
+      <c r="D78" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="15" t="n"/>
+      <c r="F78" s="15" t="n"/>
+      <c r="G78" s="15" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="15" t="n"/>
+      <c r="J78" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" s="15" t="n"/>
+      <c r="L78" s="15" t="n"/>
+      <c r="M78" s="15" t="n"/>
+      <c r="N78" s="15" t="n"/>
+      <c r="O78" s="15" t="n"/>
+      <c r="P78" s="15" t="n"/>
+      <c r="Q78" s="15" t="n"/>
+      <c r="R78" s="15" t="n"/>
+      <c r="S78" s="15" t="n"/>
+      <c r="T78" s="15" t="n"/>
+      <c r="U78" s="15" t="n"/>
+      <c r="V78" s="15" t="n"/>
+      <c r="W78" s="15" t="n"/>
+      <c r="X78" s="15" t="n"/>
+      <c r="Y78" s="15" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>キャシー・ウッド氏、5月15日の投資動向！AI半導体の有望株CBRSを2日連続で大量に買い入れ、TSMCとAMDを高値で利益確定売り</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="11" t="n"/>
+      <c r="F79" s="11" t="n"/>
+      <c r="G79" s="11" t="n"/>
+      <c r="H79" s="11" t="n"/>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="11" t="n"/>
+      <c r="M79" s="11" t="n"/>
+      <c r="N79" s="11" t="n"/>
+      <c r="O79" s="11" t="n"/>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="11" t="n"/>
+      <c r="R79" s="11" t="n"/>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="11" t="n"/>
+      <c r="U79" s="11" t="n"/>
+      <c r="V79" s="11" t="n"/>
+      <c r="W79" s="11" t="n"/>
+      <c r="X79" s="11" t="n"/>
+      <c r="Y79" s="11" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>半導体装置、AI需要がけん引 サイクルの「谷」打ち消す</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n"/>
+      <c r="D80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="15" t="n"/>
+      <c r="F80" s="15" t="n"/>
+      <c r="G80" s="15" t="n"/>
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="15" t="n"/>
+      <c r="J80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="15" t="n"/>
+      <c r="L80" s="15" t="n"/>
+      <c r="M80" s="15" t="n"/>
+      <c r="N80" s="15" t="n"/>
+      <c r="O80" s="15" t="n"/>
+      <c r="P80" s="15" t="n"/>
+      <c r="Q80" s="15" t="n"/>
+      <c r="R80" s="15" t="n"/>
+      <c r="S80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" s="15" t="n"/>
+      <c r="U80" s="15" t="n"/>
+      <c r="V80" s="15" t="n"/>
+      <c r="W80" s="15" t="n"/>
+      <c r="X80" s="15" t="n"/>
+      <c r="Y80" s="15" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>高精度アルミ加工、技術に磨き 半導体製造装置の部品供給で存在感 池松機工（大津町） 【地元発推しカンパニー】</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="11" t="n"/>
+      <c r="F81" s="11" t="n"/>
+      <c r="G81" s="11" t="n"/>
+      <c r="H81" s="11" t="n"/>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="11" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="11" t="n"/>
+      <c r="O81" s="11" t="n"/>
+      <c r="P81" s="11" t="n"/>
+      <c r="Q81" s="11" t="n"/>
+      <c r="R81" s="11" t="n"/>
+      <c r="S81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" s="11" t="n"/>
+      <c r="U81" s="11" t="n"/>
+      <c r="V81" s="11" t="n"/>
+      <c r="W81" s="11" t="n"/>
+      <c r="X81" s="11" t="n"/>
+      <c r="Y81" s="11" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>チップより急所を握る日本…世界半導体市場151兆円、シェア5%でも圧倒的影響力</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n"/>
+      <c r="D82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="15" t="n"/>
+      <c r="F82" s="15" t="n"/>
+      <c r="G82" s="15" t="n"/>
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="15" t="n"/>
+      <c r="J82" s="15" t="n"/>
+      <c r="K82" s="15" t="n"/>
+      <c r="L82" s="15" t="n"/>
+      <c r="M82" s="15" t="n"/>
+      <c r="N82" s="15" t="n"/>
+      <c r="O82" s="15" t="n"/>
+      <c r="P82" s="15" t="n"/>
+      <c r="Q82" s="15" t="n"/>
+      <c r="R82" s="15" t="n"/>
+      <c r="S82" s="15" t="n"/>
+      <c r="T82" s="15" t="n"/>
+      <c r="U82" s="15" t="n"/>
+      <c r="V82" s="15" t="n"/>
+      <c r="W82" s="15" t="n"/>
+      <c r="X82" s="15" t="n"/>
+      <c r="Y82" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>21日米エヌビディア決算の注目点は？AI・半導体相場の分岐点（土信田雅之）</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="11" t="n"/>
+      <c r="F83" s="11" t="n"/>
+      <c r="G83" s="11" t="n"/>
+      <c r="H83" s="11" t="n"/>
+      <c r="I83" s="11" t="n"/>
+      <c r="J83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="11" t="n"/>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="11" t="n"/>
+      <c r="O83" s="11" t="n"/>
+      <c r="P83" s="11" t="n"/>
+      <c r="Q83" s="11" t="n"/>
+      <c r="R83" s="11" t="n"/>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="11" t="n"/>
+      <c r="U83" s="11" t="n"/>
+      <c r="V83" s="11" t="n"/>
+      <c r="W83" s="11" t="n"/>
+      <c r="X83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>Cerebras初日68％高！AI半導体IPOが映す「NVIDIA以外」の高ベータ投資ストーリー</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n"/>
+      <c r="D84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="15" t="n"/>
+      <c r="F84" s="15" t="n"/>
+      <c r="G84" s="15" t="n"/>
+      <c r="H84" s="15" t="n"/>
+      <c r="I84" s="15" t="n"/>
+      <c r="J84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="15" t="n"/>
+      <c r="L84" s="15" t="n"/>
+      <c r="M84" s="15" t="n"/>
+      <c r="N84" s="15" t="n"/>
+      <c r="O84" s="15" t="n"/>
+      <c r="P84" s="15" t="n"/>
+      <c r="Q84" s="15" t="n"/>
+      <c r="R84" s="15" t="n"/>
+      <c r="S84" s="15" t="n"/>
+      <c r="T84" s="15" t="n"/>
+      <c r="U84" s="15" t="n"/>
+      <c r="V84" s="15" t="n"/>
+      <c r="W84" s="15" t="n"/>
+      <c r="X84" s="15" t="n"/>
+      <c r="Y84" s="15" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>［動画］どうなる？来週の米エヌビディア決算。AI・半導体相場の分岐点となるか？</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="11" t="n"/>
+      <c r="G85" s="11" t="n"/>
+      <c r="H85" s="11" t="n"/>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="11" t="n"/>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="11" t="n"/>
+      <c r="O85" s="11" t="n"/>
+      <c r="P85" s="11" t="n"/>
+      <c r="Q85" s="11" t="n"/>
+      <c r="R85" s="11" t="n"/>
+      <c r="S85" s="11" t="n"/>
+      <c r="T85" s="11" t="n"/>
+      <c r="U85" s="11" t="n"/>
+      <c r="V85" s="11" t="n"/>
+      <c r="W85" s="11" t="n"/>
+      <c r="X85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="11" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>キャシー・ウッド氏、5月14日の投資動向！AI半導体の新星CBRSを大量に買い入れ、TSMCとAMDを高値で利益確定売り、従来型医療診断株の売却を継続</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n"/>
+      <c r="D86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="15" t="n"/>
+      <c r="F86" s="15" t="n"/>
+      <c r="G86" s="15" t="n"/>
+      <c r="H86" s="15" t="n"/>
+      <c r="I86" s="15" t="n"/>
+      <c r="J86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="15" t="n"/>
+      <c r="L86" s="15" t="n"/>
+      <c r="M86" s="15" t="n"/>
+      <c r="N86" s="15" t="n"/>
+      <c r="O86" s="15" t="n"/>
+      <c r="P86" s="15" t="n"/>
+      <c r="Q86" s="15" t="n"/>
+      <c r="R86" s="15" t="n"/>
+      <c r="S86" s="15" t="n"/>
+      <c r="T86" s="15" t="n"/>
+      <c r="U86" s="15" t="n"/>
+      <c r="V86" s="15" t="n"/>
+      <c r="W86" s="15" t="n"/>
+      <c r="X86" s="15" t="n"/>
+      <c r="Y86" s="15" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>ＡＩ熱、半導体など業績けん引 中東情勢、先行きに影―上場企業の２６年３月期決算</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="11" t="n"/>
+      <c r="F87" s="11" t="n"/>
+      <c r="G87" s="11" t="n"/>
+      <c r="H87" s="11" t="n"/>
+      <c r="I87" s="11" t="n"/>
+      <c r="J87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="11" t="n"/>
+      <c r="L87" s="11" t="n"/>
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="11" t="n"/>
+      <c r="O87" s="11" t="n"/>
+      <c r="P87" s="11" t="n"/>
+      <c r="Q87" s="11" t="n"/>
+      <c r="R87" s="11" t="n"/>
+      <c r="S87" s="11" t="n"/>
+      <c r="T87" s="11" t="n"/>
+      <c r="U87" s="11" t="n"/>
+      <c r="V87" s="11" t="n"/>
+      <c r="W87" s="11" t="n"/>
+      <c r="X87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="11" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>〔潮流底流〕AI熱、半導体など業績けん引＝中東情勢、先行きに影―上場企業決算(時事通信)</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n"/>
+      <c r="D88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="15" t="n"/>
+      <c r="G88" s="15" t="n"/>
+      <c r="H88" s="15" t="n"/>
+      <c r="I88" s="15" t="n"/>
+      <c r="J88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="15" t="n"/>
+      <c r="L88" s="15" t="n"/>
+      <c r="M88" s="15" t="n"/>
+      <c r="N88" s="15" t="n"/>
+      <c r="O88" s="15" t="n"/>
+      <c r="P88" s="15" t="n"/>
+      <c r="Q88" s="15" t="n"/>
+      <c r="R88" s="15" t="n"/>
+      <c r="S88" s="15" t="n"/>
+      <c r="T88" s="15" t="n"/>
+      <c r="U88" s="15" t="n"/>
+      <c r="V88" s="15" t="n"/>
+      <c r="W88" s="15" t="n"/>
+      <c r="X88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="15" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>X線装置のリガク株、PER50倍で重い上値 半導体用途拡大も過熱感</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="11" t="n"/>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="11" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="11" t="n"/>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="11" t="n"/>
+      <c r="O89" s="11" t="n"/>
+      <c r="P89" s="11" t="n"/>
+      <c r="Q89" s="11" t="n"/>
+      <c r="R89" s="11" t="n"/>
+      <c r="S89" s="11" t="n"/>
+      <c r="T89" s="11" t="n"/>
+      <c r="U89" s="11" t="n"/>
+      <c r="V89" s="11" t="n"/>
+      <c r="W89" s="11" t="n"/>
+      <c r="X89" s="11" t="n"/>
+      <c r="Y89" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>【材料】 ホトニクスがＳ高カイ気配、ＡＩ半導体需要追い風に２６年９月期業績予想を上方修正</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n"/>
+      <c r="D90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="15" t="n"/>
+      <c r="G90" s="15" t="n"/>
+      <c r="H90" s="15" t="n"/>
+      <c r="I90" s="15" t="n"/>
+      <c r="J90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="15" t="n"/>
+      <c r="L90" s="15" t="n"/>
+      <c r="M90" s="15" t="n"/>
+      <c r="N90" s="15" t="n"/>
+      <c r="O90" s="15" t="n"/>
+      <c r="P90" s="15" t="n"/>
+      <c r="Q90" s="15" t="n"/>
+      <c r="R90" s="15" t="n"/>
+      <c r="S90" s="15" t="n"/>
+      <c r="T90" s="15" t="n"/>
+      <c r="U90" s="15" t="n"/>
+      <c r="V90" s="15" t="n"/>
+      <c r="W90" s="15" t="n"/>
+      <c r="X90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="15" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>【通期決算発表】 シキノハイテック：バーンイン装置など半導体検査装置の開発・…(フィスコ)</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="11" t="n"/>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="11" t="n"/>
+      <c r="O91" s="11" t="n"/>
+      <c r="P91" s="11" t="n"/>
+      <c r="Q91" s="11" t="n"/>
+      <c r="R91" s="11" t="n"/>
+      <c r="S91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" s="11" t="n"/>
+      <c r="U91" s="11" t="n"/>
+      <c r="V91" s="11" t="n"/>
+      <c r="W91" s="11" t="n"/>
+      <c r="X91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>世界半導体市場、30年までに1.5兆ドル ＡＩ主導＝ＴＳＭＣ（ロイター）</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="n"/>
+      <c r="D92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="15" t="n"/>
+      <c r="G92" s="15" t="n"/>
+      <c r="H92" s="15" t="n"/>
+      <c r="I92" s="15" t="n"/>
+      <c r="J92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="15" t="n"/>
+      <c r="L92" s="15" t="n"/>
+      <c r="M92" s="15" t="n"/>
+      <c r="N92" s="15" t="n"/>
+      <c r="O92" s="15" t="n"/>
+      <c r="P92" s="15" t="n"/>
+      <c r="Q92" s="15" t="n"/>
+      <c r="R92" s="15" t="n"/>
+      <c r="S92" s="15" t="n"/>
+      <c r="T92" s="15" t="n"/>
+      <c r="U92" s="15" t="n"/>
+      <c r="V92" s="15" t="n"/>
+      <c r="W92" s="15" t="n"/>
+      <c r="X92" s="15" t="n"/>
+      <c r="Y92" s="15" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>半導体･AIに引っ張られる今､乗っていきたい｢2銘柄｣</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="11" t="n"/>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="11" t="n"/>
+      <c r="I93" s="11" t="n"/>
+      <c r="J93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" s="11" t="n"/>
+      <c r="L93" s="11" t="n"/>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="11" t="n"/>
+      <c r="O93" s="11" t="n"/>
+      <c r="P93" s="11" t="n"/>
+      <c r="Q93" s="11" t="n"/>
+      <c r="R93" s="11" t="n"/>
+      <c r="S93" s="11" t="n"/>
+      <c r="T93" s="11" t="n"/>
+      <c r="U93" s="11" t="n"/>
+      <c r="V93" s="11" t="n"/>
+      <c r="W93" s="11" t="n"/>
+      <c r="X93" s="11" t="n"/>
+      <c r="Y93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>OKI、AI半導体・防衛に投資 中計で6割増 再成長へ基盤づくり</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="n"/>
+      <c r="D94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="15" t="n"/>
+      <c r="G94" s="15" t="n"/>
+      <c r="H94" s="15" t="n"/>
+      <c r="I94" s="15" t="n"/>
+      <c r="J94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="15" t="n"/>
+      <c r="L94" s="15" t="n"/>
+      <c r="M94" s="15" t="n"/>
+      <c r="N94" s="15" t="n"/>
+      <c r="O94" s="15" t="n"/>
+      <c r="P94" s="15" t="n"/>
+      <c r="Q94" s="15" t="n"/>
+      <c r="R94" s="15" t="n"/>
+      <c r="S94" s="15" t="n"/>
+      <c r="T94" s="15" t="n"/>
+      <c r="U94" s="15" t="n"/>
+      <c r="V94" s="15" t="n"/>
+      <c r="W94" s="15" t="n"/>
+      <c r="X94" s="15" t="n"/>
+      <c r="Y94" s="15" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>半導体「非先端品」、投資300億円未満も国が補助 自動車向けなど</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="11" t="n"/>
+      <c r="H95" s="11" t="n"/>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="11" t="n"/>
+      <c r="K95" s="11" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="11" t="n"/>
+      <c r="O95" s="11" t="n"/>
+      <c r="P95" s="11" t="n"/>
+      <c r="Q95" s="11" t="n"/>
+      <c r="R95" s="11" t="n"/>
+      <c r="S95" s="11" t="n"/>
+      <c r="T95" s="11" t="n"/>
+      <c r="U95" s="11" t="n"/>
+      <c r="V95" s="11" t="n"/>
+      <c r="W95" s="11" t="n"/>
+      <c r="X95" s="11" t="n"/>
+      <c r="Y95" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>AI向け半導体メーカーは市場最大のブームを牽引してきたが、ゴールドマン・サックスは新たなAI投資の台頭を見込んでいる。</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="n"/>
+      <c r="D96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="15" t="n"/>
+      <c r="F96" s="15" t="n"/>
+      <c r="G96" s="15" t="n"/>
+      <c r="H96" s="15" t="n"/>
+      <c r="I96" s="15" t="n"/>
+      <c r="J96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="15" t="n"/>
+      <c r="L96" s="15" t="n"/>
+      <c r="M96" s="15" t="n"/>
+      <c r="N96" s="15" t="n"/>
+      <c r="O96" s="15" t="n"/>
+      <c r="P96" s="15" t="n"/>
+      <c r="Q96" s="15" t="n"/>
+      <c r="R96" s="15" t="n"/>
+      <c r="S96" s="15" t="n"/>
+      <c r="T96" s="15" t="n"/>
+      <c r="U96" s="15" t="n"/>
+      <c r="V96" s="15" t="n"/>
+      <c r="W96" s="15" t="n"/>
+      <c r="X96" s="15" t="n"/>
+      <c r="Y96" s="15" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>売上高過去最高、半導体関連が好調 浜松ホトニクス、2026年3月中間決算：ニュース</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="11" t="n"/>
+      <c r="I97" s="11" t="n"/>
+      <c r="J97" s="11" t="n"/>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="11" t="n"/>
+      <c r="O97" s="11" t="n"/>
+      <c r="P97" s="11" t="n"/>
+      <c r="Q97" s="11" t="n"/>
+      <c r="R97" s="11" t="n"/>
+      <c r="S97" s="11" t="n"/>
+      <c r="T97" s="11" t="n"/>
+      <c r="U97" s="11" t="n"/>
+      <c r="V97" s="11" t="n"/>
+      <c r="W97" s="11" t="n"/>
+      <c r="X97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>〔決算〕堀場製、26年12月期連結業績予想を上方修正＝AI向け半導体需要けん引(時事通信)</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="n"/>
+      <c r="D98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="15" t="n"/>
+      <c r="F98" s="15" t="n"/>
+      <c r="G98" s="15" t="n"/>
+      <c r="H98" s="15" t="n"/>
+      <c r="I98" s="15" t="n"/>
+      <c r="J98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="15" t="n"/>
+      <c r="L98" s="15" t="n"/>
+      <c r="M98" s="15" t="n"/>
+      <c r="N98" s="15" t="n"/>
+      <c r="O98" s="15" t="n"/>
+      <c r="P98" s="15" t="n"/>
+      <c r="Q98" s="15" t="n"/>
+      <c r="R98" s="15" t="n"/>
+      <c r="S98" s="15" t="n"/>
+      <c r="T98" s="15" t="n"/>
+      <c r="U98" s="15" t="n"/>
+      <c r="V98" s="15" t="n"/>
+      <c r="W98" s="15" t="n"/>
+      <c r="X98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y98" s="15" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>【台湾】ＴＳＭＣ、313億ドルの設備投資予算を承認（NNA）</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="11" t="n"/>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="11" t="n"/>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="11" t="n"/>
+      <c r="O99" s="11" t="n"/>
+      <c r="P99" s="11" t="n"/>
+      <c r="Q99" s="11" t="n"/>
+      <c r="R99" s="11" t="n"/>
+      <c r="S99" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" s="11" t="n"/>
+      <c r="U99" s="11" t="n"/>
+      <c r="V99" s="11" t="n"/>
+      <c r="W99" s="11" t="n"/>
+      <c r="X99" s="11" t="n"/>
+      <c r="Y99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>化合物半導体検査装置の世界市場（2026年～2032年）、市場規模（SiC 検査装置、GaN 検査装置）・分析レポートを発表</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="n"/>
+      <c r="D100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="15" t="n"/>
+      <c r="F100" s="15" t="n"/>
+      <c r="G100" s="15" t="n"/>
+      <c r="H100" s="15" t="n"/>
+      <c r="I100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="15" t="n"/>
+      <c r="K100" s="15" t="n"/>
+      <c r="L100" s="15" t="n"/>
+      <c r="M100" s="15" t="n"/>
+      <c r="N100" s="15" t="n"/>
+      <c r="O100" s="15" t="n"/>
+      <c r="P100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="15" t="n"/>
+      <c r="R100" s="15" t="n"/>
+      <c r="S100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" s="15" t="n"/>
+      <c r="U100" s="15" t="n"/>
+      <c r="V100" s="15" t="n"/>
+      <c r="W100" s="15" t="n"/>
+      <c r="X100" s="15" t="n"/>
+      <c r="Y100" s="15" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>世界半導体市場、30年までに1.5兆ドル ＡＩ主導＝ＴＳＭＣ</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="n"/>
+      <c r="D101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="11" t="n"/>
+      <c r="F101" s="11" t="n"/>
+      <c r="G101" s="11" t="n"/>
+      <c r="H101" s="11" t="n"/>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="11" t="n"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="11" t="n"/>
+      <c r="O101" s="11" t="n"/>
+      <c r="P101" s="11" t="n"/>
+      <c r="Q101" s="11" t="n"/>
+      <c r="R101" s="11" t="n"/>
+      <c r="S101" s="11" t="n"/>
+      <c r="T101" s="11" t="n"/>
+      <c r="U101" s="11" t="n"/>
+      <c r="V101" s="11" t="n"/>
+      <c r="W101" s="11" t="n"/>
+      <c r="X101" s="11" t="n"/>
+      <c r="Y101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>焦点：米市場けん引の半導体株、過熱懸念も</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="n"/>
+      <c r="D102" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="15" t="n"/>
+      <c r="F102" s="15" t="n"/>
+      <c r="G102" s="15" t="n"/>
+      <c r="H102" s="15" t="n"/>
+      <c r="I102" s="15" t="n"/>
+      <c r="J102" s="15" t="n"/>
+      <c r="K102" s="15" t="n"/>
+      <c r="L102" s="15" t="n"/>
+      <c r="M102" s="15" t="n"/>
+      <c r="N102" s="15" t="n"/>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="15" t="n"/>
+      <c r="Q102" s="15" t="n"/>
+      <c r="R102" s="15" t="n"/>
+      <c r="S102" s="15" t="n"/>
+      <c r="T102" s="15" t="n"/>
+      <c r="U102" s="15" t="n"/>
+      <c r="V102" s="15" t="n"/>
+      <c r="W102" s="15" t="n"/>
+      <c r="X102" s="15" t="n"/>
+      <c r="Y102" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>決算:OKI、AI半導体と防衛事業で目指す再成長 投資額6割増の2950億円に</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="n"/>
+      <c r="D103" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="11" t="n"/>
+      <c r="F103" s="11" t="n"/>
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="11" t="n"/>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="11" t="n"/>
+      <c r="L103" s="11" t="n"/>
+      <c r="M103" s="11" t="n"/>
+      <c r="N103" s="11" t="n"/>
+      <c r="O103" s="11" t="n"/>
+      <c r="P103" s="11" t="n"/>
+      <c r="Q103" s="11" t="n"/>
+      <c r="R103" s="11" t="n"/>
+      <c r="S103" s="11" t="n"/>
+      <c r="T103" s="11" t="n"/>
+      <c r="U103" s="11" t="n"/>
+      <c r="V103" s="11" t="n"/>
+      <c r="W103" s="11" t="n"/>
+      <c r="X103" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>AI半導体相場の次なる主役？「エヌビディア対抗馬」Cerebras、上場秒読み！年内最大のIPOへ！注目すべき投資チャンスは？</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="n"/>
+      <c r="D104" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="15" t="n"/>
+      <c r="G104" s="15" t="n"/>
+      <c r="H104" s="15" t="n"/>
+      <c r="I104" s="15" t="n"/>
+      <c r="J104" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" s="15" t="n"/>
+      <c r="L104" s="15" t="n"/>
+      <c r="M104" s="15" t="n"/>
+      <c r="N104" s="15" t="n"/>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="15" t="n"/>
+      <c r="Q104" s="15" t="n"/>
+      <c r="R104" s="15" t="n"/>
+      <c r="S104" s="15" t="n"/>
+      <c r="T104" s="15" t="n"/>
+      <c r="U104" s="15" t="n"/>
+      <c r="V104" s="15" t="n"/>
+      <c r="W104" s="15" t="n"/>
+      <c r="X104" s="15" t="n"/>
+      <c r="Y104" s="15" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>26年度の日本株投資戦略 AI･半導体主導から回復が広がる【深読みリサーチ】</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="n"/>
+      <c r="D105" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="11" t="n"/>
+      <c r="F105" s="11" t="n"/>
+      <c r="G105" s="11" t="n"/>
+      <c r="H105" s="11" t="n"/>
+      <c r="I105" s="11" t="n"/>
+      <c r="J105" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="11" t="n"/>
+      <c r="L105" s="11" t="n"/>
+      <c r="M105" s="11" t="n"/>
+      <c r="N105" s="11" t="n"/>
+      <c r="O105" s="11" t="n"/>
+      <c r="P105" s="11" t="n"/>
+      <c r="Q105" s="11" t="n"/>
+      <c r="R105" s="11" t="n"/>
+      <c r="S105" s="11" t="n"/>
+      <c r="T105" s="11" t="n"/>
+      <c r="U105" s="11" t="n"/>
+      <c r="V105" s="11" t="n"/>
+      <c r="W105" s="11" t="n"/>
+      <c r="X105" s="11" t="n"/>
+      <c r="Y105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>AI・半導体・インフレヘッジ、本決算の注目ポイントを語り尽くす！マーケットを熟知する3者の勝ち筋を大公開</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="n"/>
+      <c r="D106" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="15" t="n"/>
+      <c r="G106" s="15" t="n"/>
+      <c r="H106" s="15" t="n"/>
+      <c r="I106" s="15" t="n"/>
+      <c r="J106" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" s="15" t="n"/>
+      <c r="L106" s="15" t="n"/>
+      <c r="M106" s="15" t="n"/>
+      <c r="N106" s="15" t="n"/>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="15" t="n"/>
+      <c r="Q106" s="15" t="n"/>
+      <c r="R106" s="15" t="n"/>
+      <c r="S106" s="15" t="n"/>
+      <c r="T106" s="15" t="n"/>
+      <c r="U106" s="15" t="n"/>
+      <c r="V106" s="15" t="n"/>
+      <c r="W106" s="15" t="n"/>
+      <c r="X106" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="15" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>(株)日本マイクロニクス【6871】：決算情報</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="n"/>
+      <c r="D107" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="11" t="n"/>
+      <c r="F107" s="11" t="n"/>
+      <c r="G107" s="11" t="n"/>
+      <c r="H107" s="11" t="n"/>
+      <c r="I107" s="11" t="n"/>
+      <c r="J107" s="11" t="n"/>
+      <c r="K107" s="11" t="n"/>
+      <c r="L107" s="11" t="n"/>
+      <c r="M107" s="11" t="n"/>
+      <c r="N107" s="11" t="n"/>
+      <c r="O107" s="11" t="n"/>
+      <c r="P107" s="11" t="n"/>
+      <c r="Q107" s="11" t="n"/>
+      <c r="R107" s="11" t="n"/>
+      <c r="S107" s="11" t="n"/>
+      <c r="T107" s="11" t="n"/>
+      <c r="U107" s="11" t="n"/>
+      <c r="V107" s="11" t="n"/>
+      <c r="W107" s="11" t="n"/>
+      <c r="X107" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" s="11" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>半導体の多層化進展で恩恵が期待されるラムリサーチ</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
+      <c r="G108" s="15" t="n"/>
+      <c r="H108" s="15" t="n"/>
+      <c r="I108" s="15" t="n"/>
+      <c r="J108" s="15" t="n"/>
+      <c r="K108" s="15" t="n"/>
+      <c r="L108" s="15" t="n"/>
+      <c r="M108" s="15" t="n"/>
+      <c r="N108" s="15" t="n"/>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="15" t="n"/>
+      <c r="Q108" s="15" t="n"/>
+      <c r="R108" s="15" t="n"/>
+      <c r="S108" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" s="15" t="n"/>
+      <c r="U108" s="15" t="n"/>
+      <c r="V108" s="15" t="n"/>
+      <c r="W108" s="15" t="n"/>
+      <c r="X108" s="15" t="n"/>
+      <c r="Y108" s="15" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>AI半導体検査向け…OKIサーキット、板厚2倍の配線板量産</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="n"/>
+      <c r="D109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="11" t="n"/>
+      <c r="F109" s="11" t="n"/>
+      <c r="G109" s="11" t="n"/>
+      <c r="H109" s="11" t="n"/>
+      <c r="I109" s="11" t="n"/>
+      <c r="J109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" s="11" t="n"/>
+      <c r="L109" s="11" t="n"/>
+      <c r="M109" s="11" t="n"/>
+      <c r="N109" s="11" t="n"/>
+      <c r="O109" s="11" t="n"/>
+      <c r="P109" s="11" t="n"/>
+      <c r="Q109" s="11" t="n"/>
+      <c r="R109" s="11" t="n"/>
+      <c r="S109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" s="11" t="n"/>
+      <c r="U109" s="11" t="n"/>
+      <c r="V109" s="11" t="n"/>
+      <c r="W109" s="11" t="n"/>
+      <c r="X109" s="11" t="n"/>
+      <c r="Y109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>【通期決算発表】 山一電機：半導体検査用ICソケットで世界シェアトッ…(フィスコ)</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="n"/>
+      <c r="D110" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="15" t="n"/>
+      <c r="F110" s="15" t="n"/>
+      <c r="G110" s="15" t="n"/>
+      <c r="H110" s="15" t="n"/>
+      <c r="I110" s="15" t="n"/>
+      <c r="J110" s="15" t="n"/>
+      <c r="K110" s="15" t="n"/>
+      <c r="L110" s="15" t="n"/>
+      <c r="M110" s="15" t="n"/>
+      <c r="N110" s="15" t="n"/>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="15" t="n"/>
+      <c r="Q110" s="15" t="n"/>
+      <c r="R110" s="15" t="n"/>
+      <c r="S110" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" s="15" t="n"/>
+      <c r="U110" s="15" t="n"/>
+      <c r="V110" s="15" t="n"/>
+      <c r="W110" s="15" t="n"/>
+      <c r="X110" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y110" s="15" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>AI需要続伸で世界半導体市場規模は驚異的拡大中、今年は昨年比6割以上増加か?</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="n"/>
+      <c r="D111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="11" t="n"/>
+      <c r="G111" s="11" t="n"/>
+      <c r="H111" s="11" t="n"/>
+      <c r="I111" s="11" t="n"/>
+      <c r="J111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="11" t="n"/>
+      <c r="L111" s="11" t="n"/>
+      <c r="M111" s="11" t="n"/>
+      <c r="N111" s="11" t="n"/>
+      <c r="O111" s="11" t="n"/>
+      <c r="P111" s="11" t="n"/>
+      <c r="Q111" s="11" t="n"/>
+      <c r="R111" s="11" t="n"/>
+      <c r="S111" s="11" t="n"/>
+      <c r="T111" s="11" t="n"/>
+      <c r="U111" s="11" t="n"/>
+      <c r="V111" s="11" t="n"/>
+      <c r="W111" s="11" t="n"/>
+      <c r="X111" s="11" t="n"/>
+      <c r="Y111" s="11" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>26年3月の世界半導体市場は79％増、日本も10カ月ぶりプラス成長：日本以外は2～3桁の大幅増</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="n"/>
+      <c r="D112" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="15" t="n"/>
+      <c r="F112" s="15" t="n"/>
+      <c r="G112" s="15" t="n"/>
+      <c r="H112" s="15" t="n"/>
+      <c r="I112" s="15" t="n"/>
+      <c r="J112" s="15" t="n"/>
+      <c r="K112" s="15" t="n"/>
+      <c r="L112" s="15" t="n"/>
+      <c r="M112" s="15" t="n"/>
+      <c r="N112" s="15" t="n"/>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="15" t="n"/>
+      <c r="Q112" s="15" t="n"/>
+      <c r="R112" s="15" t="n"/>
+      <c r="S112" s="15" t="n"/>
+      <c r="T112" s="15" t="n"/>
+      <c r="U112" s="15" t="n"/>
+      <c r="V112" s="15" t="n"/>
+      <c r="W112" s="15" t="n"/>
+      <c r="X112" s="15" t="n"/>
+      <c r="Y112" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>半導体市場、28年に反転 メモリー供給過剰で価格下落へ - 日経テックフォーサイト</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="11" t="n"/>
+      <c r="E113" s="11" t="n"/>
+      <c r="F113" s="11" t="n"/>
+      <c r="G113" s="11" t="n"/>
+      <c r="H113" s="11" t="n"/>
+      <c r="I113" s="11" t="n"/>
+      <c r="J113" s="11" t="n"/>
+      <c r="K113" s="11" t="n"/>
+      <c r="L113" s="11" t="n"/>
+      <c r="M113" s="11" t="n"/>
+      <c r="N113" s="11" t="n"/>
+      <c r="O113" s="11" t="n"/>
+      <c r="P113" s="11" t="n"/>
+      <c r="Q113" s="11" t="n"/>
+      <c r="R113" s="11" t="n"/>
+      <c r="S113" s="11" t="n"/>
+      <c r="T113" s="11" t="n"/>
+      <c r="U113" s="11" t="n"/>
+      <c r="V113" s="11" t="n"/>
+      <c r="W113" s="11" t="n"/>
+      <c r="X113" s="11" t="n"/>
+      <c r="Y113" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>大手ITの巨額投資から読む日米半導体｢真の注目銘柄｣とは</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="n"/>
+      <c r="D114" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="15" t="n"/>
+      <c r="F114" s="15" t="n"/>
+      <c r="G114" s="15" t="n"/>
+      <c r="H114" s="15" t="n"/>
+      <c r="I114" s="15" t="n"/>
+      <c r="J114" s="15" t="n"/>
+      <c r="K114" s="15" t="n"/>
+      <c r="L114" s="15" t="n"/>
+      <c r="M114" s="15" t="n"/>
+      <c r="N114" s="15" t="n"/>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="15" t="n"/>
+      <c r="Q114" s="15" t="n"/>
+      <c r="R114" s="15" t="n"/>
+      <c r="S114" s="15" t="n"/>
+      <c r="T114" s="15" t="n"/>
+      <c r="U114" s="15" t="n"/>
+      <c r="V114" s="15" t="n"/>
+      <c r="W114" s="15" t="n"/>
+      <c r="X114" s="15" t="n"/>
+      <c r="Y114" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>半導体関連好調、全4社が売上高過去最高に 森村グループ26年3月期決算</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="n"/>
+      <c r="D115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="11" t="n"/>
+      <c r="F115" s="11" t="n"/>
+      <c r="G115" s="11" t="n"/>
+      <c r="H115" s="11" t="n"/>
+      <c r="I115" s="11" t="n"/>
+      <c r="J115" s="11" t="n"/>
+      <c r="K115" s="11" t="n"/>
+      <c r="L115" s="11" t="n"/>
+      <c r="M115" s="11" t="n"/>
+      <c r="N115" s="11" t="n"/>
+      <c r="O115" s="11" t="n"/>
+      <c r="P115" s="11" t="n"/>
+      <c r="Q115" s="11" t="n"/>
+      <c r="R115" s="11" t="n"/>
+      <c r="S115" s="11" t="n"/>
+      <c r="T115" s="11" t="n"/>
+      <c r="U115" s="11" t="n"/>
+      <c r="V115" s="11" t="n"/>
+      <c r="W115" s="11" t="n"/>
+      <c r="X115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>AI半導体ブームの隠れた勝者？売上1兆円超え「アドバンテスト」の圧倒的シェアと事業構造の凄み（LIMO）</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="15" t="n"/>
+      <c r="F116" s="15" t="n"/>
+      <c r="G116" s="15" t="n"/>
+      <c r="H116" s="15" t="n"/>
+      <c r="I116" s="15" t="n"/>
+      <c r="J116" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" s="15" t="n"/>
+      <c r="L116" s="15" t="n"/>
+      <c r="M116" s="15" t="n"/>
+      <c r="N116" s="15" t="n"/>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="15" t="n"/>
+      <c r="Q116" s="15" t="n"/>
+      <c r="R116" s="15" t="n"/>
+      <c r="S116" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" s="15" t="n"/>
+      <c r="U116" s="15" t="n"/>
+      <c r="V116" s="15" t="n"/>
+      <c r="W116" s="15" t="n"/>
+      <c r="X116" s="15" t="n"/>
+      <c r="Y116" s="15" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>半導体市場の規模、シェア、成長、予測 [2034]</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="n"/>
+      <c r="D117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="11" t="n"/>
+      <c r="F117" s="11" t="n"/>
+      <c r="G117" s="11" t="n"/>
+      <c r="H117" s="11" t="n"/>
+      <c r="I117" s="11" t="n"/>
+      <c r="J117" s="11" t="n"/>
+      <c r="K117" s="11" t="n"/>
+      <c r="L117" s="11" t="n"/>
+      <c r="M117" s="11" t="n"/>
+      <c r="N117" s="11" t="n"/>
+      <c r="O117" s="11" t="n"/>
+      <c r="P117" s="11" t="n"/>
+      <c r="Q117" s="11" t="n"/>
+      <c r="R117" s="11" t="n"/>
+      <c r="S117" s="11" t="n"/>
+      <c r="T117" s="11" t="n"/>
+      <c r="U117" s="11" t="n"/>
+      <c r="V117" s="11" t="n"/>
+      <c r="W117" s="11" t="n"/>
+      <c r="X117" s="11" t="n"/>
+      <c r="Y117" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>アナログ半導体市場サイズ、共有|成長レポート、2034</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="15" t="n"/>
+      <c r="G118" s="15" t="n"/>
+      <c r="H118" s="15" t="n"/>
+      <c r="I118" s="15" t="n"/>
+      <c r="J118" s="15" t="n"/>
+      <c r="K118" s="15" t="n"/>
+      <c r="L118" s="15" t="n"/>
+      <c r="M118" s="15" t="n"/>
+      <c r="N118" s="15" t="n"/>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="15" t="n"/>
+      <c r="Q118" s="15" t="n"/>
+      <c r="R118" s="15" t="n"/>
+      <c r="S118" s="15" t="n"/>
+      <c r="T118" s="15" t="n"/>
+      <c r="U118" s="15" t="n"/>
+      <c r="V118" s="15" t="n"/>
+      <c r="W118" s="15" t="n"/>
+      <c r="X118" s="15" t="n"/>
+      <c r="Y118" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>化合物半導体市場規模・シェア・グローバルレポート2034</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="n"/>
+      <c r="D119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="11" t="n"/>
+      <c r="F119" s="11" t="n"/>
+      <c r="G119" s="11" t="n"/>
+      <c r="H119" s="11" t="n"/>
+      <c r="I119" s="11" t="n"/>
+      <c r="J119" s="11" t="n"/>
+      <c r="K119" s="11" t="n"/>
+      <c r="L119" s="11" t="n"/>
+      <c r="M119" s="11" t="n"/>
+      <c r="N119" s="11" t="n"/>
+      <c r="O119" s="11" t="n"/>
+      <c r="P119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q119" s="11" t="n"/>
+      <c r="R119" s="11" t="n"/>
+      <c r="S119" s="11" t="n"/>
+      <c r="T119" s="11" t="n"/>
+      <c r="U119" s="11" t="n"/>
+      <c r="V119" s="11" t="n"/>
+      <c r="W119" s="11" t="n"/>
+      <c r="X119" s="11" t="n"/>
+      <c r="Y119" s="11" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>日本の半導体市場規模、シェア、成長、2026-2034</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="n"/>
+      <c r="D120" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="15" t="n"/>
+      <c r="G120" s="15" t="n"/>
+      <c r="H120" s="15" t="n"/>
+      <c r="I120" s="15" t="n"/>
+      <c r="J120" s="15" t="n"/>
+      <c r="K120" s="15" t="n"/>
+      <c r="L120" s="15" t="n"/>
+      <c r="M120" s="15" t="n"/>
+      <c r="N120" s="15" t="n"/>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="15" t="n"/>
+      <c r="Q120" s="15" t="n"/>
+      <c r="R120" s="15" t="n"/>
+      <c r="S120" s="15" t="n"/>
+      <c r="T120" s="15" t="n"/>
+      <c r="U120" s="15" t="n"/>
+      <c r="V120" s="15" t="n"/>
+      <c r="W120" s="15" t="n"/>
+      <c r="X120" s="15" t="n"/>
+      <c r="Y120" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>航空宇宙用半導体市場規模、シェア、分析、2034年</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="n"/>
+      <c r="D121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="11" t="n"/>
+      <c r="F121" s="11" t="n"/>
+      <c r="G121" s="11" t="n"/>
+      <c r="H121" s="11" t="n"/>
+      <c r="I121" s="11" t="n"/>
+      <c r="J121" s="11" t="n"/>
+      <c r="K121" s="11" t="n"/>
+      <c r="L121" s="11" t="n"/>
+      <c r="M121" s="11" t="n"/>
+      <c r="N121" s="11" t="n"/>
+      <c r="O121" s="11" t="n"/>
+      <c r="P121" s="11" t="n"/>
+      <c r="Q121" s="11" t="n"/>
+      <c r="R121" s="11" t="n"/>
+      <c r="S121" s="11" t="n"/>
+      <c r="T121" s="11" t="n"/>
+      <c r="U121" s="11" t="n"/>
+      <c r="V121" s="11" t="n"/>
+      <c r="W121" s="11" t="n"/>
+      <c r="X121" s="11" t="n"/>
+      <c r="Y121" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>生成AIと半導体セクター（トークン急増によって計算需要が拡大中。エヌビディアの目標株価を引き上げる）</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="15" t="n"/>
+      <c r="F122" s="15" t="n"/>
+      <c r="G122" s="15" t="n"/>
+      <c r="H122" s="15" t="n"/>
+      <c r="I122" s="15" t="n"/>
+      <c r="J122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" s="15" t="n"/>
+      <c r="L122" s="15" t="n"/>
+      <c r="M122" s="15" t="n"/>
+      <c r="N122" s="15" t="n"/>
+      <c r="O122" s="15" t="n"/>
+      <c r="P122" s="15" t="n"/>
+      <c r="Q122" s="15" t="n"/>
+      <c r="R122" s="15" t="n"/>
+      <c r="S122" s="15" t="n"/>
+      <c r="T122" s="15" t="n"/>
+      <c r="U122" s="15" t="n"/>
+      <c r="V122" s="15" t="n"/>
+      <c r="W122" s="15" t="n"/>
+      <c r="X122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y122" s="15" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>自動車用電子機器市場規模・シェア｜世界的な成長、2034年</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="n"/>
+      <c r="D123" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="11" t="n"/>
+      <c r="F123" s="11" t="n"/>
+      <c r="G123" s="11" t="n"/>
+      <c r="H123" s="11" t="n"/>
+      <c r="I123" s="11" t="n"/>
+      <c r="J123" s="11" t="n"/>
+      <c r="K123" s="11" t="n"/>
+      <c r="L123" s="11" t="n"/>
+      <c r="M123" s="11" t="n"/>
+      <c r="N123" s="11" t="n"/>
+      <c r="O123" s="11" t="n"/>
+      <c r="P123" s="11" t="n"/>
+      <c r="Q123" s="11" t="n"/>
+      <c r="R123" s="11" t="n"/>
+      <c r="S123" s="11" t="n"/>
+      <c r="T123" s="11" t="n"/>
+      <c r="U123" s="11" t="n"/>
+      <c r="V123" s="11" t="n"/>
+      <c r="W123" s="11" t="n"/>
+      <c r="X123" s="11" t="n"/>
+      <c r="Y123" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>受動部品市場2035年までに839億米ドル規模へ拡大 高性能電子機器需要を追い風にCAGR6.4％成長予測</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="n"/>
+      <c r="D124" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="15" t="n"/>
+      <c r="F124" s="15" t="n"/>
+      <c r="G124" s="15" t="n"/>
+      <c r="H124" s="15" t="n"/>
+      <c r="I124" s="15" t="n"/>
+      <c r="J124" s="15" t="n"/>
+      <c r="K124" s="15" t="n"/>
+      <c r="L124" s="15" t="n"/>
+      <c r="M124" s="15" t="n"/>
+      <c r="N124" s="15" t="n"/>
+      <c r="O124" s="15" t="n"/>
+      <c r="P124" s="15" t="n"/>
+      <c r="Q124" s="15" t="n"/>
+      <c r="R124" s="15" t="n"/>
+      <c r="S124" s="15" t="n"/>
+      <c r="T124" s="15" t="n"/>
+      <c r="U124" s="15" t="n"/>
+      <c r="V124" s="15" t="n"/>
+      <c r="W124" s="15" t="n"/>
+      <c r="X124" s="15" t="n"/>
+      <c r="Y124" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>電子機器製造サービス市場規模、予測【2034年】</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="n"/>
+      <c r="D125" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="11" t="n"/>
+      <c r="F125" s="11" t="n"/>
+      <c r="G125" s="11" t="n"/>
+      <c r="H125" s="11" t="n"/>
+      <c r="I125" s="11" t="n"/>
+      <c r="J125" s="11" t="n"/>
+      <c r="K125" s="11" t="n"/>
+      <c r="L125" s="11" t="n"/>
+      <c r="M125" s="11" t="n"/>
+      <c r="N125" s="11" t="n"/>
+      <c r="O125" s="11" t="n"/>
+      <c r="P125" s="11" t="n"/>
+      <c r="Q125" s="11" t="n"/>
+      <c r="R125" s="11" t="n"/>
+      <c r="S125" s="11" t="n"/>
+      <c r="T125" s="11" t="n"/>
+      <c r="U125" s="11" t="n"/>
+      <c r="V125" s="11" t="n"/>
+      <c r="W125" s="11" t="n"/>
+      <c r="X125" s="11" t="n"/>
+      <c r="Y125" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>ポリシリコン市場規模、シェア、分析、業界見通し、2034年</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="n"/>
+      <c r="D126" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="15" t="n"/>
+      <c r="F126" s="15" t="n"/>
+      <c r="G126" s="15" t="n"/>
+      <c r="H126" s="15" t="n"/>
+      <c r="I126" s="15" t="n"/>
+      <c r="J126" s="15" t="n"/>
+      <c r="K126" s="15" t="n"/>
+      <c r="L126" s="15" t="n"/>
+      <c r="M126" s="15" t="n"/>
+      <c r="N126" s="15" t="n"/>
+      <c r="O126" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" s="15" t="n"/>
+      <c r="Q126" s="15" t="n"/>
+      <c r="R126" s="15" t="n"/>
+      <c r="S126" s="15" t="n"/>
+      <c r="T126" s="15" t="n"/>
+      <c r="U126" s="15" t="n"/>
+      <c r="V126" s="15" t="n"/>
+      <c r="W126" s="15" t="n"/>
+      <c r="X126" s="15" t="n"/>
+      <c r="Y126" s="15" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>半導体製造機器市場予測、2034</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="n"/>
+      <c r="D127" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="11" t="n"/>
+      <c r="F127" s="11" t="n"/>
+      <c r="G127" s="11" t="n"/>
+      <c r="H127" s="11" t="n"/>
+      <c r="I127" s="11" t="n"/>
+      <c r="J127" s="11" t="n"/>
+      <c r="K127" s="11" t="n"/>
+      <c r="L127" s="11" t="n"/>
+      <c r="M127" s="11" t="n"/>
+      <c r="N127" s="11" t="n"/>
+      <c r="O127" s="11" t="n"/>
+      <c r="P127" s="11" t="n"/>
+      <c r="Q127" s="11" t="n"/>
+      <c r="R127" s="11" t="n"/>
+      <c r="S127" s="11" t="n"/>
+      <c r="T127" s="11" t="n"/>
+      <c r="U127" s="11" t="n"/>
+      <c r="V127" s="11" t="n"/>
+      <c r="W127" s="11" t="n"/>
+      <c r="X127" s="11" t="n"/>
+      <c r="Y127" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>半導体製造装置用セラミック事業で研究開発／生産体制を強化、TOTO：豊前工場には「焼成棟」を建設中</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="15" t="n"/>
+      <c r="F128" s="15" t="n"/>
+      <c r="G128" s="15" t="n"/>
+      <c r="H128" s="15" t="n"/>
+      <c r="I128" s="15" t="n"/>
+      <c r="J128" s="15" t="n"/>
+      <c r="K128" s="15" t="n"/>
+      <c r="L128" s="15" t="n"/>
+      <c r="M128" s="15" t="n"/>
+      <c r="N128" s="15" t="n"/>
+      <c r="O128" s="15" t="n"/>
+      <c r="P128" s="15" t="n"/>
+      <c r="Q128" s="15" t="n"/>
+      <c r="R128" s="15" t="n"/>
+      <c r="S128" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" s="15" t="n"/>
+      <c r="U128" s="15" t="n"/>
+      <c r="V128" s="15" t="n"/>
+      <c r="W128" s="15" t="n"/>
+      <c r="X128" s="15" t="n"/>
+      <c r="Y128" s="15" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>半導体欠陥検査装置市場規模 [2034年]</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="n"/>
+      <c r="D129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="11" t="n"/>
+      <c r="F129" s="11" t="n"/>
+      <c r="G129" s="11" t="n"/>
+      <c r="H129" s="11" t="n"/>
+      <c r="I129" s="11" t="n"/>
+      <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="11" t="n"/>
+      <c r="N129" s="11" t="n"/>
+      <c r="O129" s="11" t="n"/>
+      <c r="P129" s="11" t="n"/>
+      <c r="Q129" s="11" t="n"/>
+      <c r="R129" s="11" t="n"/>
+      <c r="S129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" s="11" t="n"/>
+      <c r="U129" s="11" t="n"/>
+      <c r="V129" s="11" t="n"/>
+      <c r="W129" s="11" t="n"/>
+      <c r="X129" s="11" t="n"/>
+      <c r="Y129" s="11" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>世界の半導体工場、活発な投資へと動く | サイエンス リポート | TELESCOPE magazine</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="n"/>
+      <c r="D130" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="15" t="n"/>
+      <c r="F130" s="15" t="n"/>
+      <c r="G130" s="15" t="n"/>
+      <c r="H130" s="15" t="n"/>
+      <c r="I130" s="15" t="n"/>
+      <c r="J130" s="15" t="n"/>
+      <c r="K130" s="15" t="n"/>
+      <c r="L130" s="15" t="n"/>
+      <c r="M130" s="15" t="n"/>
+      <c r="N130" s="15" t="n"/>
+      <c r="O130" s="15" t="n"/>
+      <c r="P130" s="15" t="n"/>
+      <c r="Q130" s="15" t="n"/>
+      <c r="R130" s="15" t="n"/>
+      <c r="S130" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T130" s="15" t="n"/>
+      <c r="U130" s="15" t="n"/>
+      <c r="V130" s="15" t="n"/>
+      <c r="W130" s="15" t="n"/>
+      <c r="X130" s="15" t="n"/>
+      <c r="Y130" s="15" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>AIデータセンター需要の伸びは続くのか？ ～6万円を超える株価上昇の背景～ | 熊野 英生 | 第一ライフ資産運用経済研究所</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="n"/>
+      <c r="D131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="11" t="n"/>
+      <c r="F131" s="11" t="n"/>
+      <c r="G131" s="11" t="n"/>
+      <c r="H131" s="11" t="n"/>
+      <c r="I131" s="11" t="n"/>
+      <c r="J131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" s="11" t="n"/>
+      <c r="L131" s="11" t="n"/>
+      <c r="M131" s="11" t="n"/>
+      <c r="N131" s="11" t="n"/>
+      <c r="O131" s="11" t="n"/>
+      <c r="P131" s="11" t="n"/>
+      <c r="Q131" s="11" t="n"/>
+      <c r="R131" s="11" t="n"/>
+      <c r="S131" s="11" t="n"/>
+      <c r="T131" s="11" t="n"/>
+      <c r="U131" s="11" t="n"/>
+      <c r="V131" s="11" t="n"/>
+      <c r="W131" s="11" t="n"/>
+      <c r="X131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y131" s="11" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>NISA成長投資枠で世界の半導体株式に投資～半導体市場の未来とは？</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="n"/>
+      <c r="D132" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="15" t="n"/>
+      <c r="F132" s="15" t="n"/>
+      <c r="G132" s="15" t="n"/>
+      <c r="H132" s="15" t="n"/>
+      <c r="I132" s="15" t="n"/>
+      <c r="J132" s="15" t="n"/>
+      <c r="K132" s="15" t="n"/>
+      <c r="L132" s="15" t="n"/>
+      <c r="M132" s="15" t="n"/>
+      <c r="N132" s="15" t="n"/>
+      <c r="O132" s="15" t="n"/>
+      <c r="P132" s="15" t="n"/>
+      <c r="Q132" s="15" t="n"/>
+      <c r="R132" s="15" t="n"/>
+      <c r="S132" s="15" t="n"/>
+      <c r="T132" s="15" t="n"/>
+      <c r="U132" s="15" t="n"/>
+      <c r="V132" s="15" t="n"/>
+      <c r="W132" s="15" t="n"/>
+      <c r="X132" s="15" t="n"/>
+      <c r="Y132" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>半導体・AI関連「次の主役」を探る!?</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="n"/>
+      <c r="D133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="11" t="n"/>
+      <c r="F133" s="11" t="n"/>
+      <c r="G133" s="11" t="n"/>
+      <c r="H133" s="11" t="n"/>
+      <c r="I133" s="11" t="n"/>
+      <c r="J133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" s="11" t="n"/>
+      <c r="L133" s="11" t="n"/>
+      <c r="M133" s="11" t="n"/>
+      <c r="N133" s="11" t="n"/>
+      <c r="O133" s="11" t="n"/>
+      <c r="P133" s="11" t="n"/>
+      <c r="Q133" s="11" t="n"/>
+      <c r="R133" s="11" t="n"/>
+      <c r="S133" s="11" t="n"/>
+      <c r="T133" s="11" t="n"/>
+      <c r="U133" s="11" t="n"/>
+      <c r="V133" s="11" t="n"/>
+      <c r="W133" s="11" t="n"/>
+      <c r="X133" s="11" t="n"/>
+      <c r="Y133" s="11" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>決算レポート：東京エレクトロン（AI半導体、CPU、メモリの増産による恩恵が大きい）</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="n"/>
+      <c r="D134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="15" t="n"/>
+      <c r="F134" s="15" t="n"/>
+      <c r="G134" s="15" t="n"/>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="15" t="n"/>
+      <c r="J134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" s="15" t="n"/>
+      <c r="L134" s="15" t="n"/>
+      <c r="M134" s="15" t="n"/>
+      <c r="N134" s="15" t="n"/>
+      <c r="O134" s="15" t="n"/>
+      <c r="P134" s="15" t="n"/>
+      <c r="Q134" s="15" t="n"/>
+      <c r="R134" s="15" t="n"/>
+      <c r="S134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" s="15" t="n"/>
+      <c r="U134" s="15" t="n"/>
+      <c r="V134" s="15" t="n"/>
+      <c r="W134" s="15" t="n"/>
+      <c r="X134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y134" s="15" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>半導体検査装置向けレンズの研磨工程が稼働、生産能力2.6倍に：コニカミノルタの東京サイト八王子</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="n"/>
+      <c r="D135" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+      <c r="G135" s="11" t="n"/>
+      <c r="H135" s="11" t="n"/>
+      <c r="I135" s="11" t="n"/>
+      <c r="J135" s="11" t="n"/>
+      <c r="K135" s="11" t="n"/>
+      <c r="L135" s="11" t="n"/>
+      <c r="M135" s="11" t="n"/>
+      <c r="N135" s="11" t="n"/>
+      <c r="O135" s="11" t="n"/>
+      <c r="P135" s="11" t="n"/>
+      <c r="Q135" s="11" t="n"/>
+      <c r="R135" s="11" t="n"/>
+      <c r="S135" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T135" s="11" t="n"/>
+      <c r="U135" s="11" t="n"/>
+      <c r="V135" s="11" t="n"/>
+      <c r="W135" s="11" t="n"/>
+      <c r="X135" s="11" t="n"/>
+      <c r="Y135" s="11" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>【材料】 ＦＩＧがＳ高カイ気配、最先端ＡＩ半導体の検査工程向け自動化装置開発を材料視</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="n"/>
+      <c r="D136" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="15" t="n"/>
+      <c r="F136" s="15" t="n"/>
+      <c r="G136" s="15" t="n"/>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="15" t="n"/>
+      <c r="J136" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="15" t="n"/>
+      <c r="L136" s="15" t="n"/>
+      <c r="M136" s="15" t="n"/>
+      <c r="N136" s="15" t="n"/>
+      <c r="O136" s="15" t="n"/>
+      <c r="P136" s="15" t="n"/>
+      <c r="Q136" s="15" t="n"/>
+      <c r="R136" s="15" t="n"/>
+      <c r="S136" s="15" t="n"/>
+      <c r="T136" s="15" t="n"/>
+      <c r="U136" s="15" t="n"/>
+      <c r="V136" s="15" t="n"/>
+      <c r="W136" s="15" t="n"/>
+      <c r="X136" s="15" t="n"/>
+      <c r="Y136" s="15" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>AI半導体向け検査基板が180層に 従来上限を超える新技術とは</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="n"/>
+      <c r="D137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="11" t="n"/>
+      <c r="F137" s="11" t="n"/>
+      <c r="G137" s="11" t="n"/>
+      <c r="H137" s="11" t="n"/>
+      <c r="I137" s="11" t="n"/>
+      <c r="J137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" s="11" t="n"/>
+      <c r="L137" s="11" t="n"/>
+      <c r="M137" s="11" t="n"/>
+      <c r="N137" s="11" t="n"/>
+      <c r="O137" s="11" t="n"/>
+      <c r="P137" s="11" t="n"/>
+      <c r="Q137" s="11" t="n"/>
+      <c r="R137" s="11" t="n"/>
+      <c r="S137" s="11" t="n"/>
+      <c r="T137" s="11" t="n"/>
+      <c r="U137" s="11" t="n"/>
+      <c r="V137" s="11" t="n"/>
+      <c r="W137" s="11" t="n"/>
+      <c r="X137" s="11" t="n"/>
+      <c r="Y137" s="11" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>スペースX、AI半導体巨大工場「テラファブ」の計画判明 投資8兆円</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="n"/>
+      <c r="D138" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="15" t="n"/>
+      <c r="F138" s="15" t="n"/>
+      <c r="G138" s="15" t="n"/>
+      <c r="H138" s="15" t="n"/>
+      <c r="I138" s="15" t="n"/>
+      <c r="J138" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="15" t="n"/>
+      <c r="L138" s="15" t="n"/>
+      <c r="M138" s="15" t="n"/>
+      <c r="N138" s="15" t="n"/>
+      <c r="O138" s="15" t="n"/>
+      <c r="P138" s="15" t="n"/>
+      <c r="Q138" s="15" t="n"/>
+      <c r="R138" s="15" t="n"/>
+      <c r="S138" s="15" t="n"/>
+      <c r="T138" s="15" t="n"/>
+      <c r="U138" s="15" t="n"/>
+      <c r="V138" s="15" t="n"/>
+      <c r="W138" s="15" t="n"/>
+      <c r="X138" s="15" t="n"/>
+      <c r="Y138" s="15" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>【Applied Materials決算（2026年第2四半期）】AI半導体投資サイクルの恩恵と中国輸出規制リスクの狭間で問われる成長の持続性（Applied Materials）</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="n"/>
+      <c r="D139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="11" t="n"/>
+      <c r="F139" s="11" t="n"/>
+      <c r="G139" s="11" t="n"/>
+      <c r="H139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="11" t="n"/>
+      <c r="J139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" s="11" t="n"/>
+      <c r="L139" s="11" t="n"/>
+      <c r="M139" s="11" t="n"/>
+      <c r="N139" s="11" t="n"/>
+      <c r="O139" s="11" t="n"/>
+      <c r="P139" s="11" t="n"/>
+      <c r="Q139" s="11" t="n"/>
+      <c r="R139" s="11" t="n"/>
+      <c r="S139" s="11" t="n"/>
+      <c r="T139" s="11" t="n"/>
+      <c r="U139" s="11" t="n"/>
+      <c r="V139" s="11" t="n"/>
+      <c r="W139" s="11" t="n"/>
+      <c r="X139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y139" s="11" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>【材料】 半導体製造装置関連が一斉にカイ気配スタート、東エレクは最高値街道をまい進</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="n"/>
+      <c r="D140" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="15" t="n"/>
+      <c r="F140" s="15" t="n"/>
+      <c r="G140" s="15" t="n"/>
+      <c r="H140" s="15" t="n"/>
+      <c r="I140" s="15" t="n"/>
+      <c r="J140" s="15" t="n"/>
+      <c r="K140" s="15" t="n"/>
+      <c r="L140" s="15" t="n"/>
+      <c r="M140" s="15" t="n"/>
+      <c r="N140" s="15" t="n"/>
+      <c r="O140" s="15" t="n"/>
+      <c r="P140" s="15" t="n"/>
+      <c r="Q140" s="15" t="n"/>
+      <c r="R140" s="15" t="n"/>
+      <c r="S140" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" s="15" t="n"/>
+      <c r="U140" s="15" t="n"/>
+      <c r="V140" s="15" t="n"/>
+      <c r="W140" s="15" t="n"/>
+      <c r="X140" s="15" t="n"/>
+      <c r="Y140" s="15" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>話題株ピックアップ【夕刊】（2）：アルバック、東京鉄、半導体製造装置関連(株探ニュース)</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="n"/>
+      <c r="D141" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="11" t="n"/>
+      <c r="F141" s="11" t="n"/>
+      <c r="G141" s="11" t="n"/>
+      <c r="H141" s="11" t="n"/>
+      <c r="I141" s="11" t="n"/>
+      <c r="J141" s="11" t="n"/>
+      <c r="K141" s="11" t="n"/>
+      <c r="L141" s="11" t="n"/>
+      <c r="M141" s="11" t="n"/>
+      <c r="N141" s="11" t="n"/>
+      <c r="O141" s="11" t="n"/>
+      <c r="P141" s="11" t="n"/>
+      <c r="Q141" s="11" t="n"/>
+      <c r="R141" s="11" t="n"/>
+      <c r="S141" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T141" s="11" t="n"/>
+      <c r="U141" s="11" t="n"/>
+      <c r="V141" s="11" t="n"/>
+      <c r="W141" s="11" t="n"/>
+      <c r="X141" s="11" t="n"/>
+      <c r="Y141" s="11" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>スペースＸ、半導体巨大工場に550億ドル初期投資 総投資1190億ドルか</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="n"/>
+      <c r="D142" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="15" t="n"/>
+      <c r="F142" s="15" t="n"/>
+      <c r="G142" s="15" t="n"/>
+      <c r="H142" s="15" t="n"/>
+      <c r="I142" s="15" t="n"/>
+      <c r="J142" s="15" t="n"/>
+      <c r="K142" s="15" t="n"/>
+      <c r="L142" s="15" t="n"/>
+      <c r="M142" s="15" t="n"/>
+      <c r="N142" s="15" t="n"/>
+      <c r="O142" s="15" t="n"/>
+      <c r="P142" s="15" t="n"/>
+      <c r="Q142" s="15" t="n"/>
+      <c r="R142" s="15" t="n"/>
+      <c r="S142" s="15" t="n"/>
+      <c r="T142" s="15" t="n"/>
+      <c r="U142" s="15" t="n"/>
+      <c r="V142" s="15" t="n"/>
+      <c r="W142" s="15" t="n"/>
+      <c r="X142" s="15" t="n"/>
+      <c r="Y142" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>【材料】 ＦＩＧ、最先端ＡＩ半導体の検査工程向け自動化装置を開発</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="n"/>
+      <c r="D143" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" s="11" t="n"/>
+      <c r="F143" s="11" t="n"/>
+      <c r="G143" s="11" t="n"/>
+      <c r="H143" s="11" t="n"/>
+      <c r="I143" s="11" t="n"/>
+      <c r="J143" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" s="11" t="n"/>
+      <c r="L143" s="11" t="n"/>
+      <c r="M143" s="11" t="n"/>
+      <c r="N143" s="11" t="n"/>
+      <c r="O143" s="11" t="n"/>
+      <c r="P143" s="11" t="n"/>
+      <c r="Q143" s="11" t="n"/>
+      <c r="R143" s="11" t="n"/>
+      <c r="S143" s="11" t="n"/>
+      <c r="T143" s="11" t="n"/>
+      <c r="U143" s="11" t="n"/>
+      <c r="V143" s="11" t="n"/>
+      <c r="W143" s="11" t="n"/>
+      <c r="X143" s="11" t="n"/>
+      <c r="Y143" s="11" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>ＦＩＧ[4392]：半導体先進パッケージICテスト用自動化装置の開発に関するお知らせ 2026年5月7日(適時開示) ：日経会社情報DIGITAL</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" s="15" t="n"/>
+      <c r="F144" s="15" t="n"/>
+      <c r="G144" s="15" t="n"/>
+      <c r="H144" s="15" t="n"/>
+      <c r="I144" s="15" t="n"/>
+      <c r="J144" s="15" t="n"/>
+      <c r="K144" s="15" t="n"/>
+      <c r="L144" s="15" t="n"/>
+      <c r="M144" s="15" t="n"/>
+      <c r="N144" s="15" t="n"/>
+      <c r="O144" s="15" t="n"/>
+      <c r="P144" s="15" t="n"/>
+      <c r="Q144" s="15" t="n"/>
+      <c r="R144" s="15" t="n"/>
+      <c r="S144" s="15" t="n"/>
+      <c r="T144" s="15" t="n"/>
+      <c r="U144" s="15" t="n"/>
+      <c r="V144" s="15" t="n"/>
+      <c r="W144" s="15" t="n"/>
+      <c r="X144" s="15" t="n"/>
+      <c r="Y144" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>ラピダス・TSMC熊本第二工場で爆騰必至、半導体プラント設備工事「監視すべき20社」完全リスト</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="n"/>
+      <c r="D145" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="11" t="n"/>
+      <c r="I145" s="11" t="n"/>
+      <c r="J145" s="11" t="n"/>
+      <c r="K145" s="11" t="n"/>
+      <c r="L145" s="11" t="n"/>
+      <c r="M145" s="11" t="n"/>
+      <c r="N145" s="11" t="n"/>
+      <c r="O145" s="11" t="n"/>
+      <c r="P145" s="11" t="n"/>
+      <c r="Q145" s="11" t="n"/>
+      <c r="R145" s="11" t="n"/>
+      <c r="S145" s="11" t="n"/>
+      <c r="T145" s="11" t="n"/>
+      <c r="U145" s="11" t="n"/>
+      <c r="V145" s="11" t="n"/>
+      <c r="W145" s="11" t="n"/>
+      <c r="X145" s="11" t="n"/>
+      <c r="Y145" s="11" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>フレキシブルエレクトロニクス市場規模、シェア、収益、2034年予測</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="n"/>
+      <c r="D146" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="15" t="n"/>
+      <c r="F146" s="15" t="n"/>
+      <c r="G146" s="15" t="n"/>
+      <c r="H146" s="15" t="n"/>
+      <c r="I146" s="15" t="n"/>
+      <c r="J146" s="15" t="n"/>
+      <c r="K146" s="15" t="n"/>
+      <c r="L146" s="15" t="n"/>
+      <c r="M146" s="15" t="n"/>
+      <c r="N146" s="15" t="n"/>
+      <c r="O146" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" s="15" t="n"/>
+      <c r="Q146" s="15" t="n"/>
+      <c r="R146" s="15" t="n"/>
+      <c r="S146" s="15" t="n"/>
+      <c r="T146" s="15" t="n"/>
+      <c r="U146" s="15" t="n"/>
+      <c r="V146" s="15" t="n"/>
+      <c r="W146" s="15" t="n"/>
+      <c r="X146" s="15" t="n"/>
+      <c r="Y146" s="15" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>半導体検査用DUVレーザーの世界市場（2026年～2032年）、市場規模（CWレーザー、パルスレーザー）・分析レポートを発表</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="n"/>
+      <c r="D147" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="11" t="n"/>
+      <c r="F147" s="11" t="n"/>
+      <c r="G147" s="11" t="n"/>
+      <c r="H147" s="11" t="n"/>
+      <c r="I147" s="11" t="n"/>
+      <c r="J147" s="11" t="n"/>
+      <c r="K147" s="11" t="n"/>
+      <c r="L147" s="11" t="n"/>
+      <c r="M147" s="11" t="n"/>
+      <c r="N147" s="11" t="n"/>
+      <c r="O147" s="11" t="n"/>
+      <c r="P147" s="11" t="n"/>
+      <c r="Q147" s="11" t="n"/>
+      <c r="R147" s="11" t="n"/>
+      <c r="S147" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" s="11" t="n"/>
+      <c r="U147" s="11" t="n"/>
+      <c r="V147" s="11" t="n"/>
+      <c r="W147" s="11" t="n"/>
+      <c r="X147" s="11" t="n"/>
+      <c r="Y147" s="11" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>AI投資とは データセンター建設、半導体生産が活発に</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="n"/>
+      <c r="D148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="15" t="n"/>
+      <c r="F148" s="15" t="n"/>
+      <c r="G148" s="15" t="n"/>
+      <c r="H148" s="15" t="n"/>
+      <c r="I148" s="15" t="n"/>
+      <c r="J148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" s="15" t="n"/>
+      <c r="L148" s="15" t="n"/>
+      <c r="M148" s="15" t="n"/>
+      <c r="N148" s="15" t="n"/>
+      <c r="O148" s="15" t="n"/>
+      <c r="P148" s="15" t="n"/>
+      <c r="Q148" s="15" t="n"/>
+      <c r="R148" s="15" t="n"/>
+      <c r="S148" s="15" t="n"/>
+      <c r="T148" s="15" t="n"/>
+      <c r="U148" s="15" t="n"/>
+      <c r="V148" s="15" t="n"/>
+      <c r="W148" s="15" t="n"/>
+      <c r="X148" s="15" t="n"/>
+      <c r="Y148" s="15" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>米主要IT決算で見えたAI・半導体相場の変化（土信田雅之）</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="n"/>
+      <c r="D149" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="11" t="n"/>
+      <c r="F149" s="11" t="n"/>
+      <c r="G149" s="11" t="n"/>
+      <c r="H149" s="11" t="n"/>
+      <c r="I149" s="11" t="n"/>
+      <c r="J149" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" s="11" t="n"/>
+      <c r="L149" s="11" t="n"/>
+      <c r="M149" s="11" t="n"/>
+      <c r="N149" s="11" t="n"/>
+      <c r="O149" s="11" t="n"/>
+      <c r="P149" s="11" t="n"/>
+      <c r="Q149" s="11" t="n"/>
+      <c r="R149" s="11" t="n"/>
+      <c r="S149" s="11" t="n"/>
+      <c r="T149" s="11" t="n"/>
+      <c r="U149" s="11" t="n"/>
+      <c r="V149" s="11" t="n"/>
+      <c r="W149" s="11" t="n"/>
+      <c r="X149" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y149" s="11" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>「AI向けメモリ需要が、PC＋スマホ合計超えへ」米半導体製造装置大手ラム・リサーチ、3四半期連続で売上高最高</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="n"/>
+      <c r="D150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="15" t="n"/>
+      <c r="F150" s="15" t="n"/>
+      <c r="G150" s="15" t="n"/>
+      <c r="H150" s="15" t="n"/>
+      <c r="I150" s="15" t="n"/>
+      <c r="J150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" s="15" t="n"/>
+      <c r="L150" s="15" t="n"/>
+      <c r="M150" s="15" t="n"/>
+      <c r="N150" s="15" t="n"/>
+      <c r="O150" s="15" t="n"/>
+      <c r="P150" s="15" t="n"/>
+      <c r="Q150" s="15" t="n"/>
+      <c r="R150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T150" s="15" t="n"/>
+      <c r="U150" s="15" t="n"/>
+      <c r="V150" s="15" t="n"/>
+      <c r="W150" s="15" t="n"/>
+      <c r="X150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y150" s="15" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>ASMLのEUV露光装置、「レゴ」版は実物より入手困難</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="n"/>
+      <c r="D151" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="11" t="n"/>
+      <c r="F151" s="11" t="n"/>
+      <c r="G151" s="11" t="n"/>
+      <c r="H151" s="11" t="n"/>
+      <c r="I151" s="11" t="n"/>
+      <c r="J151" s="11" t="n"/>
+      <c r="K151" s="11" t="n"/>
+      <c r="L151" s="11" t="n"/>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="11" t="n"/>
+      <c r="O151" s="11" t="n"/>
+      <c r="P151" s="11" t="n"/>
+      <c r="Q151" s="11" t="n"/>
+      <c r="R151" s="11" t="n"/>
+      <c r="S151" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T151" s="11" t="n"/>
+      <c r="U151" s="11" t="n"/>
+      <c r="V151" s="11" t="n"/>
+      <c r="W151" s="11" t="n"/>
+      <c r="X151" s="11" t="n"/>
+      <c r="Y151" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1024,6 +6724,150 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
